--- a/Tineco/data/Tineco_sharepoint_savvy.xlsx
+++ b/Tineco/data/Tineco_sharepoint_savvy.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupefnac-my.sharepoint.com/personal/jerome_leconte_fnacdarty_com/Documents/Documents/Claude/Projects/HUB Drive constructeurs/Tineco/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9078B5EC-6A73-481E-91C0-69E78A3C3A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BADF646-C08F-4FD0-9E39-A8F96A96D21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{B73B33F9-8E6B-42AD-A804-1AC3EBCE5B72}"/>
+    <workbookView xWindow="-28908" yWindow="-108" windowWidth="29016" windowHeight="15696" xr2:uid="{B1638164-D755-4B29-9172-D6F926EE8CA0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tineco_sharepoint_savvy" sheetId="1" r:id="rId1"/>
+    <sheet name="query (10)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Tineco_sharepoint_savvy" localSheetId="0" hidden="1">Tineco_sharepoint_savvy!$A$1:$F$329</definedName>
+    <definedName name="query__10" localSheetId="0" hidden="1">'query (10)'!$A$1:$F$399</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -24,14 +24,14 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{804E6FE3-9FF0-4786-B4E8-DE7F57DEF3B7}" odcFile="C:\Users\jerom\OneDrive - FNAC\Documents\Claude\Projects\HUB Drive constructeurs\Tineco\data\Tineco_sharepoint_savvy.iqy" keepAlive="1" name="Tineco_sharepoint_savvy" type="5" refreshedVersion="8" minRefreshableVersion="3" saveData="1">
+  <connection id="1" xr16:uid="{8F4540D8-6C54-49C2-A7BB-B150AE75738D}" odcFile="C:\Users\jerom\OneDrive - FNAC\Documents\Claude\Projects\HUB Drive constructeurs\Tineco\data\query (10).iqy" keepAlive="1" name="query (10)" type="5" refreshedVersion="8" minRefreshableVersion="3" saveData="1">
     <dbPr connection="Provider=Microsoft.Office.List.OLEDB.2.0;Data Source=&quot;&quot;;ApplicationName=Excel;Version=12.0.0.0" command="&lt;LIST&gt;&lt;VIEWGUID&gt;4B095B6C-E238-4145-AEAC-58FC81495ECD&lt;/VIEWGUID&gt;&lt;LISTNAME&gt;7043100c-5b9c-457f-ab38-a4bb8df4a390&lt;/LISTNAME&gt;&lt;LISTWEB&gt;https://groupefnac.sharepoint.com/sites/SAVVY_FNACDARTY/_vti_bin&lt;/LISTWEB&gt;&lt;LISTSUBWEB&gt;&lt;/LISTSUBWEB&gt;&lt;ROOTFOLDER&gt;/sites/SAVVY%5fFNACDARTY/Documents%20partages/Tineco&lt;/ROOTFOLDER&gt;&lt;/LIST&gt;" commandType="5"/>
   </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="465">
   <si>
     <t>Modifié</t>
   </si>
@@ -69,9 +69,6 @@
     <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Carpet washer</t>
   </si>
   <si>
-    <t>RAHMOUN El Houssaine</t>
-  </si>
-  <si>
     <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Carpet washer/【For customer service】Carpet series common trouble shooting logic</t>
   </si>
   <si>
@@ -96,33 +93,33 @@
     <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Carpet washer/Carpet One/Repair Guide</t>
   </si>
   <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Carpet washer/Carpet One/Trouble Shooting</t>
+  </si>
+  <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Carpet washer/iCarpet</t>
+  </si>
+  <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Carpet washer/iCarpet/Repair Guide</t>
+  </si>
+  <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Carpet washer/iCarpet/Trouble Shooting</t>
+  </si>
+  <si>
+    <t>GOGNIAT Franck</t>
+  </si>
+  <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Carpet washer/Spare Part List</t>
+  </si>
+  <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Common SOP</t>
+  </si>
+  <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Common SOP/Pure One Station reflash process</t>
+  </si>
+  <si>
     <t>CRASTRES Thomas</t>
   </si>
   <si>
-    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Carpet washer/Carpet One/Trouble Shooting</t>
-  </si>
-  <si>
-    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Carpet washer/iCarpet</t>
-  </si>
-  <si>
-    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Carpet washer/iCarpet/Repair Guide</t>
-  </si>
-  <si>
-    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Carpet washer/iCarpet/Trouble Shooting</t>
-  </si>
-  <si>
-    <t>GOGNIAT Franck</t>
-  </si>
-  <si>
-    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Carpet washer/Spare Part List</t>
-  </si>
-  <si>
-    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Common SOP</t>
-  </si>
-  <si>
-    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Common SOP/Pure One Station reflash process</t>
-  </si>
-  <si>
     <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Floor washer</t>
   </si>
   <si>
@@ -132,6 +129,9 @@
     <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Floor washer/2.How to tear down video</t>
   </si>
   <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Floor washer/3.【for customer service】Floor washer trouble shooting - common</t>
+  </si>
+  <si>
     <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Floor washer/3.Spare Part List</t>
   </si>
   <si>
@@ -207,12 +207,18 @@
     <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Floor washer/FLOOR ONE S5 PRO2</t>
   </si>
   <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Floor washer/FLOOR ONE S5 PRO2/Instruction Book</t>
+  </si>
+  <si>
     <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Floor washer/FLOOR ONE S5 STEAM</t>
   </si>
   <si>
     <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Floor washer/FLOOR ONE S5 STEAM/Repair guidance</t>
   </si>
   <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Floor washer/FLOOR ONE S5/Instruction Book</t>
+  </si>
+  <si>
     <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Floor washer/FLOOR ONE S5/Repair Guide</t>
   </si>
   <si>
@@ -333,9 +339,18 @@
     <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Kitchen Appliance</t>
   </si>
   <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Kitchen Appliance/Trouble Shooting and Product Introduction</t>
+  </si>
+  <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Repair manual</t>
+  </si>
+  <si>
     <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Repair Manual for LMR Supplementary Model</t>
   </si>
   <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Repair manual/1.Repair manual</t>
+  </si>
+  <si>
     <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Repair Tool Operation Guide</t>
   </si>
   <si>
@@ -402,9 +417,33 @@
     <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Stick vacuum/Stick Vacuum  Spare Parts List</t>
   </si>
   <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Training files</t>
+  </si>
+  <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Training files/TO LMR(2026. Mar)</t>
+  </si>
+  <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Training files/TO LMR(2026. Mar)/3月多维</t>
+  </si>
+  <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Training files/TO LMR(2026. Mar)/CL2501 S6 Stretch Steam</t>
+  </si>
+  <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Training files/TO LMR(2026. Mar)/S9 Master – CL2467</t>
+  </si>
+  <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Training files/TO LMR(2026. Mar)/散备件列表</t>
+  </si>
+  <si>
     <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Trouble Shooting Video</t>
   </si>
   <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Trouble Shooting Video/Troble shooting Video-1</t>
+  </si>
+  <si>
+    <t>sites/SAVVY_FNACDARTY/Documents partages/Tineco/Trouble Shooting Video/Troble shooting Video-2</t>
+  </si>
+  <si>
     <t>Carpet washer</t>
   </si>
   <si>
@@ -420,6 +459,9 @@
     <t>modeles_tineco.xlsx</t>
   </si>
   <si>
+    <t>Repair manual</t>
+  </si>
+  <si>
     <t>Repair Manual for LMR Supplementary Model</t>
   </si>
   <si>
@@ -429,6 +471,9 @@
     <t>Stick vacuum</t>
   </si>
   <si>
+    <t>Training files</t>
+  </si>
+  <si>
     <t>Trouble Shooting Video</t>
   </si>
   <si>
@@ -525,6 +570,9 @@
     <t>2.How to tear down video</t>
   </si>
   <si>
+    <t>3.【for customer service】Floor washer trouble shooting - common</t>
+  </si>
+  <si>
     <t>3.Spare Part List</t>
   </si>
   <si>
@@ -660,6 +708,18 @@
     <t>S5 how to tear down .mp4</t>
   </si>
   <si>
+    <t>【bilingual】水机常见故障TS方案Floor Washer Trouble Shooting Logic 202504 update.xlsx</t>
+  </si>
+  <si>
+    <t>【for Chinese customer service 】Floor washer trouble shooting 0923 V1-Cherry补充V3定稿(2).xlsx</t>
+  </si>
+  <si>
+    <t>Floor Washer Combo&amp;Switch  Series Common  Trouble Shooting Logic.xlsx</t>
+  </si>
+  <si>
+    <t>Floor washer trouble shooting logic - common 240918.xlsx</t>
+  </si>
+  <si>
     <t>FLOOR ONE i5 STRETCH PLUS-CL2376H-02.xlsx</t>
   </si>
   <si>
@@ -855,18 +915,6 @@
     <t>global spare parts list-update2025.4.20.xlsx</t>
   </si>
   <si>
-    <t>【bilingual】水机常见故障TS方案Floor Washer Trouble Shooting Logic 202504 update.xlsx</t>
-  </si>
-  <si>
-    <t>【for Chinese customer service 】Floor washer trouble shooting 0923 V1-Cherry补充V3定稿(2).xlsx</t>
-  </si>
-  <si>
-    <t>Floor Washer Combo&amp;Switch  Series Common  Trouble Shooting Logic.xlsx</t>
-  </si>
-  <si>
-    <t>Floor washer trouble shooting logic - common 240918.xlsx</t>
-  </si>
-  <si>
     <t>Instruction Book</t>
   </si>
   <si>
@@ -894,6 +942,12 @@
     <t>New TS - S3  V1.2.xlsx</t>
   </si>
   <si>
+    <t>S3 FAQ 德法意英.xlsx</t>
+  </si>
+  <si>
+    <t>S3 FAQ 英日.xlsx</t>
+  </si>
+  <si>
     <t>Trouble shooting&amp;FAQ</t>
   </si>
   <si>
@@ -915,6 +969,9 @@
     <t>Troubleshooting S5 Combo.xlsx</t>
   </si>
   <si>
+    <t>9. CL2019 Floor One S5 Pro 2 说明书 台湾 V2 20230607.pdf</t>
+  </si>
+  <si>
     <t>Repair guidance</t>
   </si>
   <si>
@@ -927,7 +984,7 @@
     <t>S5 Steam repair guidance.pdf</t>
   </si>
   <si>
-    <t>Repair manual</t>
+    <t>9. Floor One S5 CL2019 说明书 TC(吸水模式)-20220316.pdf</t>
   </si>
   <si>
     <t>Tear Down video</t>
@@ -1062,9 +1119,15 @@
     <t>U5S</t>
   </si>
   <si>
+    <t>Yoniev U5&amp;U5S&amp;U7s Product Introduction.pptx</t>
+  </si>
+  <si>
     <t>Yoniev U7s</t>
   </si>
   <si>
+    <t>悠尼Smart Plus 使用&amp;维护.mp4</t>
+  </si>
+  <si>
     <t>Yoniev U5s repair repair guide.pptx</t>
   </si>
   <si>
@@ -1086,6 +1149,15 @@
     <t>Trouble Shooting and Product Introduction</t>
   </si>
   <si>
+    <t>Toasty one troubleshooting.xlsx</t>
+  </si>
+  <si>
+    <t>Toasty one 培训资料.pptx</t>
+  </si>
+  <si>
+    <t>1.Repair manual</t>
+  </si>
+  <si>
     <t>Floor One S5 and S6 Series Repair Manual 240619 v1.4.docx</t>
   </si>
   <si>
@@ -1098,6 +1170,45 @@
     <t>Model list.xlsx</t>
   </si>
   <si>
+    <t>Floor one i7 Fold&amp;S7 Fold  Repair Manual.docx</t>
+  </si>
+  <si>
+    <t>Floor One S5 &amp; S6 &amp; iFloor 5 Series Repair Manual.docx</t>
+  </si>
+  <si>
+    <t>Floor One S5 Steam Series repair manual V1.0.docx</t>
+  </si>
+  <si>
+    <t>Floor One S7 Pro Series Repair Manual.docx</t>
+  </si>
+  <si>
+    <t>Floor one S9&amp;S7 Artist Repair Manual.docx</t>
+  </si>
+  <si>
+    <t>Floor One Stretch S6 Series &amp;i6 Stretch &amp;S6 S7 Stretch Steam&amp;S7MAX&amp;S5MAX Repair Manual.docx</t>
+  </si>
+  <si>
+    <t>Floor one Switch S6 S7 stretch Series&amp; Breeze Repair Manual.docx</t>
+  </si>
+  <si>
+    <t>GO H2O MAX &amp;  i FLOOR Y2 Series Repair Manual.docx</t>
+  </si>
+  <si>
+    <t>iCarpet spot Repair manual.docx</t>
+  </si>
+  <si>
+    <t>iFLOOR 3 BREEZE Series Repair Manual.docx</t>
+  </si>
+  <si>
+    <t>IFLOOR 5 STEAM Series Repair Manual.docx</t>
+  </si>
+  <si>
+    <t>Yoniev U5 &amp; U5S &amp; U7s  Repair Manual.docx</t>
+  </si>
+  <si>
+    <t>悠尼2411拆机.pptx</t>
+  </si>
+  <si>
     <t>S3I3 series.mp4</t>
   </si>
   <si>
@@ -1221,6 +1332,51 @@
     <t>vs151900eu.pdf</t>
   </si>
   <si>
+    <t>TO LMR(2026. Mar)</t>
+  </si>
+  <si>
+    <t>3月多维</t>
+  </si>
+  <si>
+    <t>CL2501 S6 Stretch Steam</t>
+  </si>
+  <si>
+    <t>S6 Stretch Steam  CL2501 water circuit.pptx</t>
+  </si>
+  <si>
+    <t>S9 Artisi steam&amp;S7 stretch steam, Water and steam circuit.pptx</t>
+  </si>
+  <si>
+    <t>S9 Master – CL2467</t>
+  </si>
+  <si>
+    <t>散备件列表</t>
+  </si>
+  <si>
+    <t>2026.03多维分析---LMR.xlsx</t>
+  </si>
+  <si>
+    <t>CL2501 S6 Stretch Steam.mp4</t>
+  </si>
+  <si>
+    <t>S9 Master – CL2467.mp4</t>
+  </si>
+  <si>
+    <t>CL2467D-01、S9 Master---散备件_图片下载完成.xlsx</t>
+  </si>
+  <si>
+    <t>CL2467H-01、S7 Master---散备件_图片下载完成.xlsx</t>
+  </si>
+  <si>
+    <t>CL2501A-02、S6 Stretch Steam Plus---散备件_图片下载完成.xlsx</t>
+  </si>
+  <si>
+    <t>CL2533-01、 S7 stretch steam---散备件_图片下载完成.xlsx</t>
+  </si>
+  <si>
+    <t>CL2539-01、S9 Artist Steam Pro---散备件_图片下载完成.xlsx</t>
+  </si>
+  <si>
     <t>“Please clean the brush roller”.mp4</t>
   </si>
   <si>
@@ -1243,6 +1399,33 @@
   </si>
   <si>
     <t>Not turn on Not power on.mp4</t>
+  </si>
+  <si>
+    <t>Troble shooting Video-1</t>
+  </si>
+  <si>
+    <t>Troble shooting Video-2</t>
+  </si>
+  <si>
+    <t>False Alarm for Dirty Water Tank(2).m4v</t>
+  </si>
+  <si>
+    <t>False Alarm for Dirty Water Tank.m4v</t>
+  </si>
+  <si>
+    <t>No Steam.m4v</t>
+  </si>
+  <si>
+    <t>Not Charging.m4V</t>
+  </si>
+  <si>
+    <t>Self-Clean Not Working.m4V</t>
+  </si>
+  <si>
+    <t>Short Battery Life.mp4</t>
+  </si>
+  <si>
+    <t>Water Stains or Poor Water Pickup.m4v</t>
   </si>
 </sst>
 </file>
@@ -1820,7 +2003,7 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="Tineco_sharepoint_savvy" backgroundRefresh="0" connectionId="1" xr16:uid="{0923E6BF-ACB4-4351-B193-352BFE16E9E4}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="query (10)" backgroundRefresh="0" connectionId="1" xr16:uid="{4F6AA628-8D40-4336-9A65-942F691E2D62}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="7">
     <queryTableFields count="6">
       <queryTableField id="6" name="Nom" tableColumnId="1"/>
@@ -1835,15 +2018,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{329756E3-A07D-401C-BE76-11B9A2400AFE}" name="Tableau_Tineco_sharepoint_savvy" displayName="Tableau_Tineco_sharepoint_savvy" ref="A1:F329" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F329" xr:uid="{329756E3-A07D-401C-BE76-11B9A2400AFE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CCCA972E-3D78-4C70-B2C7-9DCFF1A717BA}" name="Tableau_query__10" displayName="Tableau_query__10" ref="A1:F399" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:F399" xr:uid="{CCCA972E-3D78-4C70-B2C7-9DCFF1A717BA}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{DD993C64-879B-479A-BB50-77477580F651}" uniqueName="FileLeafRef" name="Nom" queryTableFieldId="6"/>
-    <tableColumn id="2" xr3:uid="{5DDA2A28-1A34-43DA-8E25-13361D40C24C}" uniqueName="Modified" name="Modifié" queryTableFieldId="1" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{63FCFD59-8E74-446B-BB2D-C6B0554529FE}" uniqueName="Editor" name="Modifié par" queryTableFieldId="3" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{1624A7CC-8D63-4675-A301-179244338A58}" uniqueName="_x005f_x0024_Resources_x005f_x003a_core_x005f_x002c_Signoff_Status" name="État de validation" queryTableFieldId="2" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{88E58F98-C817-4EF9-9347-59B8D0A24742}" uniqueName="FSObjType" name="Type d'élément" queryTableFieldId="5" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{F06C7597-3010-4F83-AF15-EDF73703F36D}" uniqueName="FileDirRef" name="Chemin d'accès" queryTableFieldId="4" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{B4688A1A-F4A1-4A5B-8665-97477F906847}" uniqueName="FileLeafRef" name="Nom" queryTableFieldId="6"/>
+    <tableColumn id="2" xr3:uid="{4F4E99F2-F5BA-4AB8-9D43-79052FCAA1BA}" uniqueName="Modified" name="Modifié" queryTableFieldId="1" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{39F49C57-F086-4CE3-AE5F-2F55FC358DF4}" uniqueName="Editor" name="Modifié par" queryTableFieldId="3" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{579D6282-1CAC-43DD-BA63-719C8FA8F25A}" uniqueName="_x005f_x0024_Resources_x005f_x003a_core_x005f_x002c_Signoff_Status" name="État de validation" queryTableFieldId="2" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{4FA3108C-FC29-4446-9CF5-B75F55F5D7D3}" uniqueName="FSObjType" name="Type d'élément" queryTableFieldId="5" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{8D5D3C2B-4F83-4DFB-B597-70D633EF08EC}" uniqueName="FileDirRef" name="Chemin d'accès" queryTableFieldId="4" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2165,19 +2348,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B5408B-18CA-4B83-95EC-AF39DA3D49C8}">
-  <dimension ref="A1:F329"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A65979AC-D561-4529-B7EB-9AEF93BF7717}">
+  <dimension ref="A1:F399"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="80.61328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.53515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.4609375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.69140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="80.61328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="80.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="80.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -2197,9 +2380,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="B2" s="2">
         <v>45902.363287037035</v>
@@ -2215,9 +2398,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B3" s="2">
         <v>45902.363287037035</v>
@@ -2233,9 +2416,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="B4" s="2">
         <v>45902.363287037035</v>
@@ -2251,9 +2434,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B5" s="2">
         <v>45902.363287037035</v>
@@ -2269,9 +2452,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B6" s="2">
         <v>46007.394513888888</v>
@@ -2287,12 +2470,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B7" s="2">
-        <v>45902.363287037035</v>
+        <v>46304.67701388889</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>6</v>
@@ -2305,9 +2488,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B8" s="2">
         <v>45902.363287037035</v>
@@ -2323,9 +2506,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="B9" s="2">
         <v>45902.363287037035</v>
@@ -2341,9 +2524,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B10" s="2">
         <v>45902.363287037035</v>
@@ -2359,12 +2542,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="B11" s="2">
-        <v>45902.363321759258</v>
+        <v>46304.677499999998</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>6</v>
@@ -2374,15 +2557,15 @@
         <v>8</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B12" s="2">
-        <v>45902.363321759258</v>
+        <v>45902.363287037035</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>6</v>
@@ -2392,12 +2575,12 @@
         <v>8</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="B13" s="2">
         <v>45902.363321759258</v>
@@ -2413,9 +2596,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="B14" s="2">
         <v>45902.363321759258</v>
@@ -2431,9 +2614,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B15" s="2">
         <v>45902.363321759258</v>
@@ -2449,9 +2632,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B16" s="2">
         <v>45902.363321759258</v>
@@ -2467,30 +2650,30 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B17" s="2">
-        <v>45922.289895833332</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="B18" s="2">
-        <v>45902.363333333335</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>6</v>
@@ -2500,69 +2683,69 @@
         <v>8</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B19" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.676388888889</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="B20" s="2">
-        <v>45902.38957175926</v>
+        <v>45902.363333333335</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="B21" s="2">
-        <v>45902.38958333333</v>
+        <v>45902.363333333335</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="B22" s="2">
-        <v>45902.389594907407</v>
+        <v>45902.38957175926</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>6</v>
@@ -2572,15 +2755,15 @@
         <v>10</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="B23" s="2">
-        <v>45902.38957175926</v>
+        <v>45902.38958333333</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>6</v>
@@ -2590,15 +2773,15 @@
         <v>10</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="B24" s="2">
-        <v>45902.38957175926</v>
+        <v>46304.676365740743</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>6</v>
@@ -2608,48 +2791,48 @@
         <v>10</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B25" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.676377314812</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="B26" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.676377314812</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B27" s="2">
         <v>45902.363333333335</v>
@@ -2662,69 +2845,69 @@
         <v>8</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B28" s="2">
-        <v>45902.389606481483</v>
+        <v>45902.363333333335</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="B29" s="2">
-        <v>45902.389618055553</v>
+        <v>45902.363333333335</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B30" s="2">
-        <v>46001.681018518517</v>
+        <v>45902.389606481483</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="B31" s="2">
-        <v>45902.38962962963</v>
+        <v>45902.389618055553</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>6</v>
@@ -2734,87 +2917,87 @@
         <v>10</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="B32" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.676377314812</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="B33" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.676388888889</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="B34" s="2">
-        <v>45902.38962962963</v>
+        <v>45902.363333333335</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B35" s="2">
-        <v>45902.389618055553</v>
+        <v>45902.363333333335</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B36" s="2">
-        <v>45902.389722222222</v>
+        <v>45902.38962962963</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>6</v>
@@ -2824,33 +3007,33 @@
         <v>10</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="B37" s="2">
-        <v>45919.571053240739</v>
+        <v>45902.389618055553</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B38" s="2">
-        <v>45902.366157407407</v>
+        <v>46304.676388888889</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>6</v>
@@ -2860,33 +3043,33 @@
         <v>10</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B39" s="2">
-        <v>45902.363321759258</v>
+        <v>45919.571053240739</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="B40" s="2">
-        <v>45902.366655092592</v>
+        <v>46304.676400462966</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>6</v>
@@ -2896,33 +3079,33 @@
         <v>10</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="B41" s="2">
-        <v>45902.366875</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B42" s="2">
-        <v>45902.40011574074</v>
+        <v>46304.676400462966</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>6</v>
@@ -2932,15 +3115,15 @@
         <v>10</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="B43" s="2">
-        <v>45994.386435185188</v>
+        <v>46304.676400462966</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>6</v>
@@ -2950,66 +3133,66 @@
         <v>10</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="B44" s="2">
-        <v>46212.616435185184</v>
+        <v>45902.40011574074</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B45" s="2">
-        <v>45902.363298611112</v>
+        <v>46304.676400462966</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="B46" s="2">
-        <v>45902.363298611112</v>
+        <v>46212.616435185184</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="B47" s="2">
         <v>45902.363298611112</v>
@@ -3022,15 +3205,15 @@
         <v>8</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B48" s="2">
-        <v>45902.363298611112</v>
+        <v>46304.676516203705</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>6</v>
@@ -3040,12 +3223,12 @@
         <v>8</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="B49" s="2">
         <v>45902.363298611112</v>
@@ -3058,12 +3241,12 @@
         <v>8</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B50" s="2">
         <v>45902.363298611112</v>
@@ -3076,12 +3259,12 @@
         <v>8</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="B51" s="2">
         <v>45902.363298611112</v>
@@ -3094,12 +3277,12 @@
         <v>8</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B52" s="2">
         <v>45902.363298611112</v>
@@ -3112,12 +3295,12 @@
         <v>8</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="B53" s="2">
         <v>45902.363298611112</v>
@@ -3130,12 +3313,12 @@
         <v>8</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B54" s="2">
         <v>45902.363298611112</v>
@@ -3148,12 +3331,12 @@
         <v>8</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B55" s="2">
         <v>45902.363298611112</v>
@@ -3166,12 +3349,12 @@
         <v>8</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="B56" s="2">
         <v>45902.363298611112</v>
@@ -3184,12 +3367,12 @@
         <v>8</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="B57" s="2">
         <v>45902.363298611112</v>
@@ -3202,12 +3385,12 @@
         <v>8</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B58" s="2">
         <v>45902.363298611112</v>
@@ -3220,12 +3403,12 @@
         <v>8</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="B59" s="2">
         <v>45902.363298611112</v>
@@ -3238,12 +3421,12 @@
         <v>8</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B60" s="2">
         <v>45902.363298611112</v>
@@ -3256,12 +3439,12 @@
         <v>8</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="B61" s="2">
         <v>45902.363298611112</v>
@@ -3274,12 +3457,12 @@
         <v>8</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B62" s="2">
         <v>45902.363298611112</v>
@@ -3292,12 +3475,12 @@
         <v>8</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="B63" s="2">
         <v>45902.363298611112</v>
@@ -3310,12 +3493,12 @@
         <v>8</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B64" s="2">
         <v>45902.363298611112</v>
@@ -3328,12 +3511,12 @@
         <v>8</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="B65" s="2">
         <v>45902.363298611112</v>
@@ -3346,12 +3529,12 @@
         <v>8</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B66" s="2">
         <v>45902.363298611112</v>
@@ -3364,411 +3547,411 @@
         <v>8</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="B67" s="2">
-        <v>46212.61645833333</v>
+        <v>45902.363298611112</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B68" s="2">
-        <v>46212.616469907407</v>
+        <v>45902.363298611112</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="B69" s="2">
-        <v>46212.616481481484</v>
+        <v>45902.363298611112</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="B70" s="2">
-        <v>46212.61650462963</v>
+        <v>46212.61645833333</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="B71" s="2">
-        <v>46212.616631944446</v>
+        <v>46304.676412037035</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="B72" s="2">
-        <v>46212.616585648146</v>
+        <v>46304.676412037035</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B73" s="2">
-        <v>46212.616608796299</v>
+        <v>46304.676412037035</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B74" s="2">
-        <v>46212.616620370369</v>
+        <v>46304.676423611112</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="B75" s="2">
-        <v>46212.616678240738</v>
+        <v>46304.676423611112</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D75" s="4"/>
       <c r="E75" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B76" s="2">
-        <v>46212.616701388892</v>
+        <v>46304.676435185182</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B77" s="2">
-        <v>46212.616736111115</v>
+        <v>46304.676435185182</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="B78" s="2">
-        <v>46212.616747685184</v>
+        <v>46304.676446759258</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="B79" s="2">
-        <v>46212.616932870369</v>
+        <v>46304.676446759258</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="B80" s="2">
-        <v>46212.616805555554</v>
+        <v>46304.676458333335</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="B81" s="2">
-        <v>46212.61681712963</v>
+        <v>46304.676458333335</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="B82" s="2">
-        <v>46212.6169212963</v>
+        <v>46304.676469907405</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B83" s="2">
-        <v>46212.616863425923</v>
+        <v>46304.676469907405</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="B84" s="2">
-        <v>46212.6169212963</v>
+        <v>46304.676481481481</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="B85" s="2">
-        <v>46212.616979166669</v>
+        <v>46304.676481481481</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D85" s="4"/>
       <c r="E85" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B86" s="2">
-        <v>46212.616956018515</v>
+        <v>46304.676481481481</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B87" s="2">
-        <v>46212.616956018515</v>
+        <v>46304.676493055558</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="B88" s="2">
-        <v>46212.616990740738</v>
+        <v>46304.676493055558</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D88" s="4"/>
       <c r="E88" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B89" s="2">
-        <v>45902.401180555556</v>
+        <v>46304.676493055558</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>6</v>
@@ -3778,15 +3961,15 @@
         <v>10</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="B90" s="2">
-        <v>45902.400972222225</v>
+        <v>46304.676493055558</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>6</v>
@@ -3796,33 +3979,33 @@
         <v>10</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B91" s="2">
-        <v>45919.434965277775</v>
+        <v>46304.676504629628</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="B92" s="2">
-        <v>45919.551759259259</v>
+        <v>45902.401180555556</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>6</v>
@@ -3832,108 +4015,108 @@
         <v>10</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B93" s="2">
-        <v>45919.45484953704</v>
+        <v>45902.400972222225</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B94" s="2">
-        <v>45978.458993055552</v>
+        <v>46304.676516203705</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="B95" s="2">
-        <v>45992.610578703701</v>
+        <v>46304.676516203705</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B96" s="2">
-        <v>45924.463206018518</v>
+        <v>46304.676504629628</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B97" s="2">
-        <v>45924.464004629626</v>
+        <v>46304.676504629628</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="D97" s="4"/>
       <c r="E97" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B98" s="2">
-        <v>45994.357488425929</v>
+        <v>45919.434965277775</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="4" t="s">
@@ -3943,15 +4126,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B99" s="2">
-        <v>45924.463240740741</v>
+        <v>45919.551759259259</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="D99" s="4"/>
       <c r="E99" s="4" t="s">
@@ -3961,15 +4144,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B100" s="2">
-        <v>45978.477222222224</v>
+        <v>45919.45484953704</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="4" t="s">
@@ -3979,12 +4162,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="B101" s="2">
-        <v>45978.481157407405</v>
+        <v>45978.458993055552</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>35</v>
@@ -3997,15 +4180,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="B102" s="2">
-        <v>45978.510960648149</v>
+        <v>45992.610578703701</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D102" s="4"/>
       <c r="E102" s="4" t="s">
@@ -4015,15 +4198,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B103" s="2">
-        <v>45978.475162037037</v>
+        <v>45924.463206018518</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D103" s="4"/>
       <c r="E103" s="4" t="s">
@@ -4033,15 +4216,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="B104" s="2">
-        <v>45978.514270833337</v>
+        <v>45924.464004629626</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D104" s="4"/>
       <c r="E104" s="4" t="s">
@@ -4051,15 +4234,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B105" s="2">
-        <v>46063.464942129627</v>
+        <v>45994.357488425929</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D105" s="4"/>
       <c r="E105" s="4" t="s">
@@ -4069,15 +4252,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B106" s="2">
-        <v>45978.515821759262</v>
+        <v>45924.463240740741</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D106" s="4"/>
       <c r="E106" s="4" t="s">
@@ -4087,12 +4270,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B107" s="2">
-        <v>45978.516793981478</v>
+        <v>45978.477222222224</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>35</v>
@@ -4105,12 +4288,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="B108" s="2">
-        <v>45978.519814814812</v>
+        <v>45978.481157407405</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>35</v>
@@ -4123,15 +4306,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B109" s="2">
-        <v>46002.626273148147</v>
+        <v>45978.510960648149</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D109" s="4"/>
       <c r="E109" s="4" t="s">
@@ -4141,15 +4324,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="B110" s="2">
-        <v>46106.568333333336</v>
+        <v>45978.475162037037</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D110" s="4"/>
       <c r="E110" s="4" t="s">
@@ -4159,12 +4342,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B111" s="2">
-        <v>45978.521099537036</v>
+        <v>45978.514270833337</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>35</v>
@@ -4177,30 +4360,30 @@
         <v>33</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B112" s="2">
-        <v>45902.363321759258</v>
+        <v>46063.464942129627</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D112" s="4"/>
       <c r="E112" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="B113" s="2">
-        <v>45978.525243055556</v>
+        <v>45978.515821759262</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>35</v>
@@ -4213,15 +4396,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B114" s="2">
-        <v>45902.378946759258</v>
+        <v>45978.516793981478</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D114" s="4"/>
       <c r="E114" s="4" t="s">
@@ -4231,12 +4414,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="B115" s="2">
-        <v>45978.533425925925</v>
+        <v>45978.519814814812</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>35</v>
@@ -4249,15 +4432,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B116" s="2">
-        <v>45978.532442129632</v>
+        <v>46002.626273148147</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D116" s="4"/>
       <c r="E116" s="4" t="s">
@@ -4267,15 +4450,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="B117" s="2">
-        <v>45978.534699074073</v>
+        <v>46106.568333333336</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D117" s="4"/>
       <c r="E117" s="4" t="s">
@@ -4285,15 +4468,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B118" s="2">
-        <v>46079.479467592595</v>
+        <v>45978.521099537036</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D118" s="4"/>
       <c r="E118" s="4" t="s">
@@ -4303,9 +4486,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B119" s="2">
         <v>45902.363321759258</v>
@@ -4321,12 +4504,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B120" s="2">
-        <v>45978.551851851851</v>
+        <v>45978.525243055556</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>35</v>
@@ -4339,15 +4522,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="B121" s="2">
-        <v>45922.561759259261</v>
+        <v>45902.378946759258</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="D121" s="4"/>
       <c r="E121" s="4" t="s">
@@ -4357,15 +4540,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B122" s="2">
-        <v>46006.362638888888</v>
+        <v>45978.533425925925</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D122" s="4"/>
       <c r="E122" s="4" t="s">
@@ -4375,12 +4558,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="B123" s="2">
-        <v>45978.639745370368</v>
+        <v>45978.532442129632</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>35</v>
@@ -4393,12 +4576,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B124" s="2">
-        <v>45978.639085648145</v>
+        <v>45978.534699074073</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>35</v>
@@ -4411,15 +4594,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B125" s="2">
-        <v>45978.643483796295</v>
+        <v>46079.479467592595</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D125" s="4"/>
       <c r="E125" s="4" t="s">
@@ -4429,30 +4612,30 @@
         <v>33</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="B126" s="2">
-        <v>45978.6094212963</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="D126" s="4"/>
       <c r="E126" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B127" s="2">
-        <v>45978.556597222225</v>
+        <v>45978.551851851851</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>35</v>
@@ -4465,15 +4648,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B128" s="2">
-        <v>45924.356793981482</v>
+        <v>45922.561759259261</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D128" s="4"/>
       <c r="E128" s="4" t="s">
@@ -4483,15 +4666,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B129" s="2">
-        <v>45922.591979166667</v>
+        <v>46006.362638888888</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="D129" s="4"/>
       <c r="E129" s="4" t="s">
@@ -4501,12 +4684,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B130" s="2">
-        <v>45978.646481481483</v>
+        <v>45978.639745370368</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>35</v>
@@ -4519,12 +4702,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="B131" s="2">
-        <v>45978.645856481482</v>
+        <v>45978.639085648145</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>35</v>
@@ -4537,12 +4720,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B132" s="2">
-        <v>45978.548854166664</v>
+        <v>45978.643483796295</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>35</v>
@@ -4555,15 +4738,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="B133" s="2">
-        <v>45924.398611111108</v>
+        <v>45978.6094212963</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D133" s="4"/>
       <c r="E133" s="4" t="s">
@@ -4573,15 +4756,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="B134" s="2">
-        <v>46146.536192129628</v>
+        <v>45978.556597222225</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D134" s="4"/>
       <c r="E134" s="4" t="s">
@@ -4591,15 +4774,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B135" s="2">
-        <v>46007.636423611111</v>
+        <v>45924.356793981482</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D135" s="4"/>
       <c r="E135" s="4" t="s">
@@ -4609,15 +4792,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B136" s="2">
-        <v>45924.386296296296</v>
+        <v>45922.591979166667</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="4" t="s">
@@ -4627,12 +4810,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="B137" s="2">
-        <v>45978.48</v>
+        <v>45978.646481481483</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>35</v>
@@ -4645,12 +4828,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="B138" s="2">
-        <v>45978.480914351851</v>
+        <v>45978.645856481482</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>35</v>
@@ -4663,12 +4846,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="B139" s="2">
-        <v>45978.433333333334</v>
+        <v>45978.548854166664</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>35</v>
@@ -4681,15 +4864,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B140" s="2">
-        <v>45924.549872685187</v>
+        <v>45924.398611111108</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D140" s="4"/>
       <c r="E140" s="4" t="s">
@@ -4699,12 +4882,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="B141" s="2">
-        <v>46147.608518518522</v>
+        <v>46146.536192129628</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>9</v>
@@ -4717,15 +4900,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="B142" s="2">
-        <v>45902.381377314814</v>
+        <v>46007.636423611111</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4" t="s">
@@ -4735,15 +4918,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="B143" s="2">
-        <v>46002.379004629627</v>
+        <v>45924.386296296296</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D143" s="4"/>
       <c r="E143" s="4" t="s">
@@ -4753,12 +4936,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="B144" s="2">
-        <v>45978.647916666669</v>
+        <v>45978.48</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>35</v>
@@ -4771,15 +4954,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="B145" s="2">
-        <v>46204.447546296295</v>
+        <v>45978.480914351851</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D145" s="4"/>
       <c r="E145" s="4" t="s">
@@ -4789,15 +4972,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="B146" s="2">
-        <v>45994.402824074074</v>
+        <v>45978.433333333334</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D146" s="4"/>
       <c r="E146" s="4" t="s">
@@ -4807,15 +4990,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="B147" s="2">
-        <v>45902.381469907406</v>
+        <v>45924.549872685187</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="D147" s="4"/>
       <c r="E147" s="4" t="s">
@@ -4825,15 +5008,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="B148" s="2">
-        <v>45978.531724537039</v>
+        <v>46147.608518518522</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D148" s="4"/>
       <c r="E148" s="4" t="s">
@@ -4843,15 +5026,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="B149" s="2">
-        <v>45978.535324074073</v>
+        <v>45902.381377314814</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="D149" s="4"/>
       <c r="E149" s="4" t="s">
@@ -4861,84 +5044,84 @@
         <v>33</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="B150" s="2">
-        <v>45902.363344907404</v>
+        <v>46002.379004629627</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D150" s="4"/>
       <c r="E150" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="B151" s="2">
-        <v>45902.389236111114</v>
+        <v>45978.647916666669</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D151" s="4"/>
       <c r="E151" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="B152" s="2">
-        <v>45902.39025462963</v>
+        <v>46204.447546296295</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="B153" s="2">
-        <v>45902.390300925923</v>
+        <v>45994.402824074074</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D153" s="4"/>
       <c r="E153" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="B154" s="2">
-        <v>45902.390324074076</v>
+        <v>45902.381469907406</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>6</v>
@@ -4948,69 +5131,69 @@
         <v>10</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B155" s="2">
-        <v>45902.389270833337</v>
+        <v>45978.531724537039</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="B156" s="2">
-        <v>46079.469768518517</v>
+        <v>45978.535324074073</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="B157" s="2">
-        <v>46079.469930555555</v>
+        <v>45902.363344907404</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D157" s="4"/>
       <c r="E157" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="B158" s="2">
-        <v>45902.377847222226</v>
+        <v>45902.389236111114</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>6</v>
@@ -5020,15 +5203,15 @@
         <v>10</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="B159" s="2">
-        <v>45902.378240740742</v>
+        <v>45902.39025462963</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>6</v>
@@ -5038,123 +5221,123 @@
         <v>10</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="B160" s="2">
-        <v>45902.363321759258</v>
+        <v>45902.390300925923</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D160" s="4"/>
       <c r="E160" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>147</v>
+        <v>292</v>
       </c>
       <c r="B161" s="2">
-        <v>45902.363321759258</v>
+        <v>45902.390324074076</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B162" s="2">
-        <v>45902.363321759258</v>
+        <v>45902.389270833337</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>280</v>
+        <v>225</v>
       </c>
       <c r="B163" s="2">
-        <v>45902.401562500003</v>
+        <v>46079.469768518517</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D163" s="4"/>
       <c r="E163" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>281</v>
+        <v>226</v>
       </c>
       <c r="B164" s="2">
-        <v>45902.401192129626</v>
+        <v>46079.469930555555</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D164" s="4"/>
       <c r="E164" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>282</v>
+        <v>227</v>
       </c>
       <c r="B165" s="2">
-        <v>45902.363333333335</v>
+        <v>45902.377847222226</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D165" s="4"/>
       <c r="E165" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>283</v>
+        <v>228</v>
       </c>
       <c r="B166" s="2">
-        <v>45902.389293981483</v>
+        <v>45902.378240740742</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>6</v>
@@ -5164,105 +5347,105 @@
         <v>10</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B167" s="2">
-        <v>45902.389733796299</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>285</v>
+        <v>162</v>
       </c>
       <c r="B168" s="2">
-        <v>45902.389733796299</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B169" s="2">
-        <v>45902.389097222222</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="B170" s="2">
-        <v>45902.363321759258</v>
+        <v>45902.401562500003</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D170" s="4"/>
       <c r="E170" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
-        <v>147</v>
+        <v>297</v>
       </c>
       <c r="B171" s="2">
-        <v>45902.363321759258</v>
+        <v>46304.676516203705</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D171" s="4"/>
       <c r="E171" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="B172" s="2">
-        <v>45902.363321759258</v>
+        <v>45902.363333333335</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>6</v>
@@ -5272,69 +5455,69 @@
         <v>8</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="B173" s="2">
-        <v>45902.363321759258</v>
+        <v>45902.389293981483</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D173" s="4"/>
       <c r="E173" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>147</v>
+        <v>300</v>
       </c>
       <c r="B174" s="2">
-        <v>45902.363321759258</v>
+        <v>46304.676527777781</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D174" s="4"/>
       <c r="E174" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="B175" s="2">
-        <v>45902.363321759258</v>
+        <v>45902.389733796299</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D175" s="4"/>
       <c r="E175" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="B176" s="2">
-        <v>45902.389062499999</v>
+        <v>46304.676550925928</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>6</v>
@@ -5344,15 +5527,15 @@
         <v>10</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="B177" s="2">
-        <v>45902.38921296296</v>
+        <v>46304.676550925928</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>6</v>
@@ -5362,15 +5545,15 @@
         <v>10</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B178" s="2">
-        <v>45902.389236111114</v>
+        <v>46304.676550925928</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>6</v>
@@ -5380,66 +5563,66 @@
         <v>10</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B179" s="2">
-        <v>45902.389236111114</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D179" s="4"/>
       <c r="E179" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>292</v>
+        <v>162</v>
       </c>
       <c r="B180" s="2">
-        <v>45902.389247685183</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D180" s="4"/>
       <c r="E180" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="B181" s="2">
-        <v>45902.38925925926</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C181" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D181" s="4"/>
       <c r="E181" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="B182" s="2">
         <v>45902.363321759258</v>
@@ -5452,12 +5635,12 @@
         <v>8</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
-        <v>294</v>
+        <v>162</v>
       </c>
       <c r="B183" s="2">
         <v>45902.363321759258</v>
@@ -5470,33 +5653,33 @@
         <v>8</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>295</v>
       </c>
       <c r="B184" s="2">
-        <v>45902.389270833337</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C184" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D184" s="4"/>
       <c r="E184" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B185" s="2">
-        <v>45902.389270833337</v>
+        <v>45902.389062499999</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>6</v>
@@ -5506,15 +5689,15 @@
         <v>10</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B186" s="2">
-        <v>45902.389270833337</v>
+        <v>45902.38921296296</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>6</v>
@@ -5524,69 +5707,69 @@
         <v>10</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="B187" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.676562499997</v>
       </c>
       <c r="C187" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D187" s="4"/>
       <c r="E187" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="B188" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.676562499997</v>
       </c>
       <c r="C188" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D188" s="4"/>
       <c r="E188" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="B189" s="2">
-        <v>45902.363344907404</v>
+        <v>46304.676562499997</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D189" s="4"/>
       <c r="E189" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="B190" s="2">
-        <v>45902.389675925922</v>
+        <v>46304.676574074074</v>
       </c>
       <c r="C190" s="3" t="s">
         <v>6</v>
@@ -5596,33 +5779,33 @@
         <v>10</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B191" s="2">
-        <v>45902.38962962963</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C191" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D191" s="4"/>
       <c r="E191" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B192" s="2">
-        <v>45902.389652777776</v>
+        <v>46304.676585648151</v>
       </c>
       <c r="C192" s="3" t="s">
         <v>6</v>
@@ -5632,33 +5815,33 @@
         <v>10</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="B193" s="2">
-        <v>45902.389699074076</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C193" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D193" s="4"/>
       <c r="E193" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B194" s="2">
-        <v>45902.389710648145</v>
+        <v>45902.389270833337</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>6</v>
@@ -5668,15 +5851,15 @@
         <v>10</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
-        <v>190</v>
+        <v>315</v>
       </c>
       <c r="B195" s="2">
-        <v>45902.389722222222</v>
+        <v>45902.389270833337</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>6</v>
@@ -5686,15 +5869,15 @@
         <v>10</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>283</v>
+        <v>316</v>
       </c>
       <c r="B196" s="2">
-        <v>45902.390243055554</v>
+        <v>45902.389270833337</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>6</v>
@@ -5704,15 +5887,15 @@
         <v>10</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B197" s="2">
-        <v>45902.390740740739</v>
+        <v>46304.676585648151</v>
       </c>
       <c r="C197" s="3" t="s">
         <v>6</v>
@@ -5722,69 +5905,69 @@
         <v>10</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>208</v>
+        <v>298</v>
       </c>
       <c r="B198" s="2">
-        <v>45902.390752314815</v>
+        <v>45902.363333333335</v>
       </c>
       <c r="C198" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D198" s="4"/>
       <c r="E198" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
-        <v>306</v>
+        <v>142</v>
       </c>
       <c r="B199" s="2">
-        <v>45902.389120370368</v>
+        <v>45902.363333333335</v>
       </c>
       <c r="C199" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D199" s="4"/>
       <c r="E199" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B200" s="2">
-        <v>45902.389120370368</v>
+        <v>45902.363344907404</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D200" s="4"/>
       <c r="E200" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="B201" s="2">
-        <v>45902.389189814814</v>
+        <v>46304.67659722222</v>
       </c>
       <c r="C201" s="3" t="s">
         <v>6</v>
@@ -5794,15 +5977,15 @@
         <v>10</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B202" s="2">
-        <v>45902.389224537037</v>
+        <v>45902.38962962963</v>
       </c>
       <c r="C202" s="3" t="s">
         <v>6</v>
@@ -5812,51 +5995,51 @@
         <v>10</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
-        <v>147</v>
+        <v>321</v>
       </c>
       <c r="B203" s="2">
-        <v>45902.363321759258</v>
+        <v>46304.67659722222</v>
       </c>
       <c r="C203" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D203" s="4"/>
       <c r="E203" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>279</v>
+        <v>322</v>
       </c>
       <c r="B204" s="2">
-        <v>45902.363321759258</v>
+        <v>46304.676608796297</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D204" s="4"/>
       <c r="E204" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="B205" s="2">
-        <v>45902.389317129629</v>
+        <v>46304.676620370374</v>
       </c>
       <c r="C205" s="3" t="s">
         <v>6</v>
@@ -5866,15 +6049,15 @@
         <v>10</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>311</v>
+        <v>206</v>
       </c>
       <c r="B206" s="2">
-        <v>45902.389293981483</v>
+        <v>46304.676620370374</v>
       </c>
       <c r="C206" s="3" t="s">
         <v>6</v>
@@ -5884,15 +6067,15 @@
         <v>10</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="B207" s="2">
-        <v>45902.389317129629</v>
+        <v>45902.390243055554</v>
       </c>
       <c r="C207" s="3" t="s">
         <v>6</v>
@@ -5902,51 +6085,51 @@
         <v>10</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>147</v>
+        <v>324</v>
       </c>
       <c r="B208" s="2">
-        <v>45902.363321759258</v>
+        <v>45902.390740740739</v>
       </c>
       <c r="C208" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D208" s="4"/>
       <c r="E208" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
-        <v>279</v>
+        <v>224</v>
       </c>
       <c r="B209" s="2">
-        <v>45902.363321759258</v>
+        <v>45902.390752314815</v>
       </c>
       <c r="C209" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D209" s="4"/>
       <c r="E209" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B210" s="2">
-        <v>45902.389351851853</v>
+        <v>46304.676631944443</v>
       </c>
       <c r="C210" s="3" t="s">
         <v>6</v>
@@ -5956,15 +6139,15 @@
         <v>10</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.4">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B211" s="2">
-        <v>45902.389351851853</v>
+        <v>46304.676631944443</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>6</v>
@@ -5974,15 +6157,15 @@
         <v>10</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.4">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B212" s="2">
-        <v>45902.389351851853</v>
+        <v>46304.676631944443</v>
       </c>
       <c r="C212" s="3" t="s">
         <v>6</v>
@@ -5992,15 +6175,15 @@
         <v>10</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.4">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B213" s="2">
-        <v>45902.389363425929</v>
+        <v>46304.676655092589</v>
       </c>
       <c r="C213" s="3" t="s">
         <v>6</v>
@@ -6010,12 +6193,12 @@
         <v>10</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.4">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B214" s="2">
         <v>45902.363321759258</v>
@@ -6028,12 +6211,12 @@
         <v>8</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.4">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B215" s="2">
         <v>45902.363321759258</v>
@@ -6046,15 +6229,15 @@
         <v>8</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.4">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B216" s="2">
-        <v>45902.389305555553</v>
+        <v>46304.676666666666</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>6</v>
@@ -6064,15 +6247,15 @@
         <v>10</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B217" s="2">
-        <v>45902.389317129629</v>
+        <v>46304.676666666666</v>
       </c>
       <c r="C217" s="3" t="s">
         <v>6</v>
@@ -6082,15 +6265,15 @@
         <v>10</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.4">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B218" s="2">
-        <v>45902.389340277776</v>
+        <v>46304.676678240743</v>
       </c>
       <c r="C218" s="3" t="s">
         <v>6</v>
@@ -6100,12 +6283,12 @@
         <v>10</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.4">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B219" s="2">
         <v>45902.363321759258</v>
@@ -6118,12 +6301,12 @@
         <v>8</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B220" s="2">
         <v>45902.363321759258</v>
@@ -6136,15 +6319,15 @@
         <v>8</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B221" s="2">
-        <v>45902.389363425929</v>
+        <v>45902.389351851853</v>
       </c>
       <c r="C221" s="3" t="s">
         <v>6</v>
@@ -6154,15 +6337,15 @@
         <v>10</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="B222" s="2">
-        <v>45902.389363425929</v>
+        <v>46304.676678240743</v>
       </c>
       <c r="C222" s="3" t="s">
         <v>6</v>
@@ -6172,15 +6355,15 @@
         <v>10</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B223" s="2">
-        <v>45902.389363425929</v>
+        <v>46304.676689814813</v>
       </c>
       <c r="C223" s="3" t="s">
         <v>6</v>
@@ -6190,15 +6373,15 @@
         <v>10</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B224" s="2">
-        <v>45902.389363425929</v>
+        <v>46304.676701388889</v>
       </c>
       <c r="C224" s="3" t="s">
         <v>6</v>
@@ -6208,51 +6391,51 @@
         <v>10</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
-        <v>324</v>
+        <v>162</v>
       </c>
       <c r="B225" s="2">
-        <v>45902.389386574076</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C225" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D225" s="4"/>
       <c r="E225" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.4">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>197</v>
+        <v>295</v>
       </c>
       <c r="B226" s="2">
-        <v>45902.38480324074</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D226" s="4"/>
       <c r="E226" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.4">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
-        <v>204</v>
+        <v>336</v>
       </c>
       <c r="B227" s="2">
-        <v>45902.381712962961</v>
+        <v>45902.389305555553</v>
       </c>
       <c r="C227" s="3" t="s">
         <v>6</v>
@@ -6262,87 +6445,87 @@
         <v>10</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>147</v>
+        <v>337</v>
       </c>
       <c r="B228" s="2">
-        <v>45902.363321759258</v>
+        <v>45902.389317129629</v>
       </c>
       <c r="C228" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D228" s="4"/>
       <c r="E228" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
-        <v>279</v>
+        <v>338</v>
       </c>
       <c r="B229" s="2">
-        <v>45902.363321759258</v>
+        <v>46304.676712962966</v>
       </c>
       <c r="C229" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D229" s="4"/>
       <c r="E229" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>325</v>
+        <v>162</v>
       </c>
       <c r="B230" s="2">
-        <v>45902.389398148145</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D230" s="4"/>
       <c r="E230" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
-        <v>326</v>
+        <v>295</v>
       </c>
       <c r="B231" s="2">
-        <v>45902.389386574076</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C231" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D231" s="4"/>
       <c r="E231" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="B232" s="2">
-        <v>45902.389398148145</v>
+        <v>45902.389363425929</v>
       </c>
       <c r="C232" s="3" t="s">
         <v>6</v>
@@ -6352,51 +6535,51 @@
         <v>10</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
-        <v>147</v>
+        <v>340</v>
       </c>
       <c r="B233" s="2">
-        <v>45902.363321759258</v>
+        <v>45902.389363425929</v>
       </c>
       <c r="C233" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D233" s="4"/>
       <c r="E233" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>279</v>
+        <v>341</v>
       </c>
       <c r="B234" s="2">
-        <v>45902.363333333335</v>
+        <v>45902.389363425929</v>
       </c>
       <c r="C234" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D234" s="4"/>
       <c r="E234" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B235" s="2">
-        <v>45902.389421296299</v>
+        <v>46304.676712962966</v>
       </c>
       <c r="C235" s="3" t="s">
         <v>6</v>
@@ -6406,15 +6589,15 @@
         <v>10</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="B236" s="2">
-        <v>45902.389409722222</v>
+        <v>46304.676712962966</v>
       </c>
       <c r="C236" s="3" t="s">
         <v>6</v>
@@ -6424,87 +6607,87 @@
         <v>10</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
-        <v>330</v>
+        <v>213</v>
       </c>
       <c r="B237" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.676736111112</v>
       </c>
       <c r="C237" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D237" s="4"/>
       <c r="E237" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.4">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>141</v>
+        <v>220</v>
       </c>
       <c r="B238" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.676793981482</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D238" s="4"/>
       <c r="E238" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
-        <v>331</v>
+        <v>162</v>
       </c>
       <c r="B239" s="2">
-        <v>45902.389444444445</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C239" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D239" s="4"/>
       <c r="E239" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>332</v>
+        <v>295</v>
       </c>
       <c r="B240" s="2">
-        <v>45902.389479166668</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D240" s="4"/>
       <c r="E240" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="B241" s="2">
-        <v>45902.389467592591</v>
+        <v>46304.676747685182</v>
       </c>
       <c r="C241" s="3" t="s">
         <v>6</v>
@@ -6514,87 +6697,87 @@
         <v>10</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>147</v>
+        <v>345</v>
       </c>
       <c r="B242" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.676747685182</v>
       </c>
       <c r="C242" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D242" s="4"/>
       <c r="E242" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
-        <v>279</v>
+        <v>346</v>
       </c>
       <c r="B243" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.676747685182</v>
       </c>
       <c r="C243" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D243" s="4"/>
       <c r="E243" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>284</v>
+        <v>162</v>
       </c>
       <c r="B244" s="2">
-        <v>45902.389548611114</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C244" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D244" s="4"/>
       <c r="E244" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
-        <v>334</v>
+        <v>295</v>
       </c>
       <c r="B245" s="2">
-        <v>45902.389467592591</v>
+        <v>45902.363333333335</v>
       </c>
       <c r="C245" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D245" s="4"/>
       <c r="E245" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B246" s="2">
-        <v>45902.389479166668</v>
+        <v>46304.676759259259</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>6</v>
@@ -6604,15 +6787,15 @@
         <v>10</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B247" s="2">
-        <v>45902.384953703702</v>
+        <v>46304.676759259259</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>6</v>
@@ -6622,51 +6805,51 @@
         <v>10</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B248" s="2">
-        <v>45902.385011574072</v>
+        <v>45902.363333333335</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D248" s="4"/>
       <c r="E248" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
-        <v>338</v>
+        <v>156</v>
       </c>
       <c r="B249" s="2">
-        <v>45910.377997685187</v>
+        <v>45902.363333333335</v>
       </c>
       <c r="C249" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D249" s="4"/>
       <c r="E249" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="B250" s="2">
-        <v>45910.378194444442</v>
+        <v>46304.676770833335</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>6</v>
@@ -6676,48 +6859,48 @@
         <v>10</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B251" s="2">
-        <v>45922.564409722225</v>
+        <v>46304.676770833335</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D251" s="4"/>
       <c r="E251" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B252" s="2">
-        <v>45922.564432870371</v>
+        <v>46304.676782407405</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D252" s="4"/>
       <c r="E252" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
-        <v>342</v>
+        <v>162</v>
       </c>
       <c r="B253" s="2">
         <v>45902.363333333335</v>
@@ -6730,12 +6913,12 @@
         <v>8</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>343</v>
+        <v>295</v>
       </c>
       <c r="B254" s="2">
         <v>45902.363333333335</v>
@@ -6748,51 +6931,51 @@
         <v>8</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
-        <v>147</v>
+        <v>300</v>
       </c>
       <c r="B255" s="2">
-        <v>45902.363344907404</v>
+        <v>46304.676793981482</v>
       </c>
       <c r="C255" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D255" s="4"/>
       <c r="E255" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>141</v>
+        <v>353</v>
       </c>
       <c r="B256" s="2">
-        <v>45902.363344907404</v>
+        <v>46304.676793981482</v>
       </c>
       <c r="C256" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D256" s="4"/>
       <c r="E256" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="B257" s="2">
-        <v>45902.390625</v>
+        <v>46304.676805555559</v>
       </c>
       <c r="C257" s="3" t="s">
         <v>6</v>
@@ -6802,15 +6985,15 @@
         <v>10</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="B258" s="2">
-        <v>45902.390439814815</v>
+        <v>46304.676805555559</v>
       </c>
       <c r="C258" s="3" t="s">
         <v>6</v>
@@ -6820,15 +7003,15 @@
         <v>10</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="B259" s="2">
-        <v>45902.390451388892</v>
+        <v>46304.676817129628</v>
       </c>
       <c r="C259" s="3" t="s">
         <v>6</v>
@@ -6838,15 +7021,15 @@
         <v>10</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="B260" s="2">
-        <v>45902.390462962961</v>
+        <v>45910.377997685187</v>
       </c>
       <c r="C260" s="3" t="s">
         <v>6</v>
@@ -6856,15 +7039,15 @@
         <v>10</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="B261" s="2">
-        <v>45902.390567129631</v>
+        <v>46304.676817129628</v>
       </c>
       <c r="C261" s="3" t="s">
         <v>6</v>
@@ -6874,15 +7057,15 @@
         <v>10</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="B262" s="2">
-        <v>45902.389537037037</v>
+        <v>46304.676828703705</v>
       </c>
       <c r="C262" s="3" t="s">
         <v>6</v>
@@ -6892,15 +7075,15 @@
         <v>10</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
-        <v>206</v>
+        <v>360</v>
       </c>
       <c r="B263" s="2">
-        <v>45902.389525462961</v>
+        <v>46304.676840277774</v>
       </c>
       <c r="C263" s="3" t="s">
         <v>6</v>
@@ -6910,15 +7093,15 @@
         <v>10</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B264" s="2">
-        <v>45902.363298611112</v>
+        <v>45902.363333333335</v>
       </c>
       <c r="C264" s="3" t="s">
         <v>6</v>
@@ -6928,15 +7111,15 @@
         <v>8</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B265" s="2">
-        <v>45902.367800925924</v>
+        <v>46304.676874999997</v>
       </c>
       <c r="C265" s="3" t="s">
         <v>6</v>
@@ -6946,33 +7129,33 @@
         <v>10</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="B266" s="2">
-        <v>45902.368171296293</v>
+        <v>45902.363333333335</v>
       </c>
       <c r="C266" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D266" s="4"/>
       <c r="E266" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
-        <v>192</v>
+        <v>364</v>
       </c>
       <c r="B267" s="2">
-        <v>45902.367951388886</v>
+        <v>46304.676932870374</v>
       </c>
       <c r="C267" s="3" t="s">
         <v>6</v>
@@ -6982,51 +7165,51 @@
         <v>10</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="B268" s="2">
-        <v>45902.368287037039</v>
+        <v>45902.363344907404</v>
       </c>
       <c r="C268" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D268" s="4"/>
       <c r="E268" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="B269" s="2">
-        <v>45902.368333333332</v>
+        <v>45902.363344907404</v>
       </c>
       <c r="C269" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D269" s="4"/>
       <c r="E269" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>197</v>
+        <v>365</v>
       </c>
       <c r="B270" s="2">
-        <v>45902.373356481483</v>
+        <v>46304.676840277774</v>
       </c>
       <c r="C270" s="3" t="s">
         <v>6</v>
@@ -7036,15 +7219,15 @@
         <v>10</v>
       </c>
       <c r="F270" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="B271" s="2">
-        <v>45902.368518518517</v>
+        <v>45902.390439814815</v>
       </c>
       <c r="C271" s="3" t="s">
         <v>6</v>
@@ -7054,15 +7237,15 @@
         <v>10</v>
       </c>
       <c r="F271" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="B272" s="2">
-        <v>45902.368460648147</v>
+        <v>45902.390451388892</v>
       </c>
       <c r="C272" s="3" t="s">
         <v>6</v>
@@ -7072,33 +7255,33 @@
         <v>10</v>
       </c>
       <c r="F272" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B273" s="2">
-        <v>45910.557627314818</v>
+        <v>46304.676840277774</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D273" s="4"/>
       <c r="E273" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F273" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B274" s="2">
-        <v>45902.365208333336</v>
+        <v>46304.676863425928</v>
       </c>
       <c r="C274" s="3" t="s">
         <v>6</v>
@@ -7108,15 +7291,15 @@
         <v>10</v>
       </c>
       <c r="F274" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="B275" s="2">
-        <v>45902.366828703707</v>
+        <v>46304.676874999997</v>
       </c>
       <c r="C275" s="3" t="s">
         <v>6</v>
@@ -7126,30 +7309,30 @@
         <v>10</v>
       </c>
       <c r="F275" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>357</v>
+        <v>222</v>
       </c>
       <c r="B276" s="2">
-        <v>45902.363321759258</v>
+        <v>46304.676921296297</v>
       </c>
       <c r="C276" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D276" s="4"/>
       <c r="E276" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F276" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="B277" s="2">
         <v>45902.363298611112</v>
@@ -7162,51 +7345,51 @@
         <v>8</v>
       </c>
       <c r="F277" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="B278" s="2">
-        <v>45902.363310185188</v>
+        <v>46304.676932870374</v>
       </c>
       <c r="C278" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D278" s="4"/>
       <c r="E278" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F278" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="B279" s="2">
-        <v>45902.363310185188</v>
+        <v>46304.676932870374</v>
       </c>
       <c r="C279" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D279" s="4"/>
       <c r="E279" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F279" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="B280" s="2">
-        <v>45902.363310185188</v>
+        <v>46304.677349537036</v>
       </c>
       <c r="C280" s="3" t="s">
         <v>6</v>
@@ -7216,159 +7399,159 @@
         <v>8</v>
       </c>
       <c r="F280" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="B281" s="2">
-        <v>45902.363310185188</v>
+        <v>46304.676944444444</v>
       </c>
       <c r="C281" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D281" s="4"/>
       <c r="E281" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F281" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="B282" s="2">
-        <v>45902.363310185188</v>
+        <v>46304.67695601852</v>
       </c>
       <c r="C282" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D282" s="4"/>
       <c r="E282" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F282" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
-        <v>364</v>
+        <v>208</v>
       </c>
       <c r="B283" s="2">
-        <v>45902.363310185188</v>
+        <v>46304.67696759259</v>
       </c>
       <c r="C283" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D283" s="4"/>
       <c r="E283" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F283" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
-        <v>365</v>
+        <v>209</v>
       </c>
       <c r="B284" s="2">
-        <v>45902.363310185188</v>
+        <v>46304.676979166667</v>
       </c>
       <c r="C284" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D284" s="4"/>
       <c r="E284" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F284" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
-        <v>366</v>
+        <v>210</v>
       </c>
       <c r="B285" s="2">
-        <v>45902.363310185188</v>
+        <v>46304.676979166667</v>
       </c>
       <c r="C285" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D285" s="4"/>
       <c r="E285" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>367</v>
+        <v>213</v>
       </c>
       <c r="B286" s="2">
-        <v>45902.363310185188</v>
+        <v>46304.676990740743</v>
       </c>
       <c r="C286" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D286" s="4"/>
       <c r="E286" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F286" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
-        <v>368</v>
+        <v>219</v>
       </c>
       <c r="B287" s="2">
-        <v>45902.363310185188</v>
+        <v>46304.676990740743</v>
       </c>
       <c r="C287" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D287" s="4"/>
       <c r="E287" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B288" s="2">
-        <v>45902.363310185188</v>
+        <v>46304.67701388889</v>
       </c>
       <c r="C288" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D288" s="4"/>
       <c r="E288" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F288" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B289" s="2">
-        <v>45902.399976851855</v>
+        <v>46304.67701388889</v>
       </c>
       <c r="C289" s="3" t="s">
         <v>6</v>
@@ -7378,15 +7561,15 @@
         <v>10</v>
       </c>
       <c r="F289" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>371</v>
+        <v>202</v>
       </c>
       <c r="B290" s="2">
-        <v>45902.400023148148</v>
+        <v>46304.677048611113</v>
       </c>
       <c r="C290" s="3" t="s">
         <v>6</v>
@@ -7396,15 +7579,15 @@
         <v>10</v>
       </c>
       <c r="F290" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
-        <v>372</v>
+        <v>203</v>
       </c>
       <c r="B291" s="2">
-        <v>45902.400069444448</v>
+        <v>46304.677106481482</v>
       </c>
       <c r="C291" s="3" t="s">
         <v>6</v>
@@ -7414,36 +7597,36 @@
         <v>10</v>
       </c>
       <c r="F291" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>141</v>
+        <v>379</v>
       </c>
       <c r="B292" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.677118055559</v>
       </c>
       <c r="C292" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D292" s="4"/>
       <c r="E292" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F292" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
-        <v>373</v>
+        <v>204</v>
       </c>
       <c r="B293" s="2">
-        <v>45922.290520833332</v>
+        <v>46304.677118055559</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D293" s="4"/>
       <c r="E293" s="4" t="s">
@@ -7453,12 +7636,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>374</v>
+        <v>297</v>
       </c>
       <c r="B294" s="2">
-        <v>45902.389548611114</v>
+        <v>46304.677141203705</v>
       </c>
       <c r="C294" s="3" t="s">
         <v>6</v>
@@ -7471,12 +7654,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B295" s="2">
-        <v>45902.389548611114</v>
+        <v>46304.677141203705</v>
       </c>
       <c r="C295" s="3" t="s">
         <v>6</v>
@@ -7489,12 +7672,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>376</v>
       </c>
       <c r="B296" s="2">
-        <v>45902.399571759262</v>
+        <v>46304.677152777775</v>
       </c>
       <c r="C296" s="3" t="s">
         <v>6</v>
@@ -7504,33 +7687,33 @@
         <v>10</v>
       </c>
       <c r="F296" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B297" s="2">
-        <v>46003.558807870373</v>
+        <v>46304.677175925928</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D297" s="4"/>
       <c r="E297" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F297" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>378</v>
+        <v>207</v>
       </c>
       <c r="B298" s="2">
-        <v>45902.399710648147</v>
+        <v>46304.677187499998</v>
       </c>
       <c r="C298" s="3" t="s">
         <v>6</v>
@@ -7540,15 +7723,15 @@
         <v>10</v>
       </c>
       <c r="F298" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
-        <v>379</v>
+        <v>208</v>
       </c>
       <c r="B299" s="2">
-        <v>45902.399733796294</v>
+        <v>46304.677187499998</v>
       </c>
       <c r="C299" s="3" t="s">
         <v>6</v>
@@ -7558,15 +7741,15 @@
         <v>10</v>
       </c>
       <c r="F299" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B300" s="2">
-        <v>45902.399756944447</v>
+        <v>46304.677199074074</v>
       </c>
       <c r="C300" s="3" t="s">
         <v>6</v>
@@ -7576,15 +7759,15 @@
         <v>10</v>
       </c>
       <c r="F300" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
-        <v>381</v>
+        <v>210</v>
       </c>
       <c r="B301" s="2">
-        <v>45902.399791666663</v>
+        <v>46304.677210648151</v>
       </c>
       <c r="C301" s="3" t="s">
         <v>6</v>
@@ -7594,15 +7777,15 @@
         <v>10</v>
       </c>
       <c r="F301" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B302" s="2">
-        <v>45902.399814814817</v>
+        <v>46304.677222222221</v>
       </c>
       <c r="C302" s="3" t="s">
         <v>6</v>
@@ -7612,15 +7795,15 @@
         <v>10</v>
       </c>
       <c r="F302" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B303" s="2">
-        <v>45902.399826388886</v>
+        <v>46304.677233796298</v>
       </c>
       <c r="C303" s="3" t="s">
         <v>6</v>
@@ -7630,15 +7813,15 @@
         <v>10</v>
       </c>
       <c r="F303" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B304" s="2">
-        <v>45902.399837962963</v>
+        <v>46304.677245370367</v>
       </c>
       <c r="C304" s="3" t="s">
         <v>6</v>
@@ -7648,69 +7831,69 @@
         <v>10</v>
       </c>
       <c r="F304" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
-        <v>141</v>
+        <v>386</v>
       </c>
       <c r="B305" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.677245370367</v>
       </c>
       <c r="C305" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D305" s="4"/>
       <c r="E305" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F305" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B306" s="2">
-        <v>46076.695277777777</v>
+        <v>46304.677256944444</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D306" s="4"/>
       <c r="E306" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F306" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
-        <v>141</v>
+        <v>388</v>
       </c>
       <c r="B307" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.677256944444</v>
       </c>
       <c r="C307" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D307" s="4"/>
       <c r="E307" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F307" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B308" s="2">
-        <v>45902.389594907407</v>
+        <v>46304.67732638889</v>
       </c>
       <c r="C308" s="3" t="s">
         <v>6</v>
@@ -7720,69 +7903,69 @@
         <v>10</v>
       </c>
       <c r="F308" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
-        <v>141</v>
+        <v>377</v>
       </c>
       <c r="B309" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.67732638889</v>
       </c>
       <c r="C309" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D309" s="4"/>
       <c r="E309" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F309" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B310" s="2">
-        <v>46003.559641203705</v>
+        <v>46304.677337962959</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D310" s="4"/>
       <c r="E310" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F310" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
-        <v>141</v>
+        <v>391</v>
       </c>
       <c r="B311" s="2">
-        <v>45902.363333333335</v>
+        <v>46304.677349537036</v>
       </c>
       <c r="C311" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D311" s="4"/>
       <c r="E311" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F311" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B312" s="2">
-        <v>45902.38958333333</v>
+        <v>45902.365208333336</v>
       </c>
       <c r="C312" s="3" t="s">
         <v>6</v>
@@ -7792,51 +7975,51 @@
         <v>10</v>
       </c>
       <c r="F312" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
-        <v>141</v>
+        <v>393</v>
       </c>
       <c r="B313" s="2">
-        <v>45902.363333333335</v>
+        <v>45902.366828703707</v>
       </c>
       <c r="C313" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D313" s="4"/>
       <c r="E313" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F313" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B314" s="2">
-        <v>45902.38957175926</v>
+        <v>45902.363321759258</v>
       </c>
       <c r="C314" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D314" s="4"/>
       <c r="E314" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F314" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
-        <v>141</v>
+        <v>395</v>
       </c>
       <c r="B315" s="2">
-        <v>45902.363333333335</v>
+        <v>45902.363298611112</v>
       </c>
       <c r="C315" s="3" t="s">
         <v>6</v>
@@ -7846,213 +8029,213 @@
         <v>8</v>
       </c>
       <c r="F315" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B316" s="2">
-        <v>45902.389594907407</v>
+        <v>45902.363310185188</v>
       </c>
       <c r="C316" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D316" s="4"/>
       <c r="E316" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F316" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B317" s="2">
-        <v>45902.389594907407</v>
+        <v>45902.363310185188</v>
       </c>
       <c r="C317" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D317" s="4"/>
       <c r="E317" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F317" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B318" s="2">
-        <v>45902.399918981479</v>
+        <v>45902.363310185188</v>
       </c>
       <c r="C318" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D318" s="4"/>
       <c r="E318" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F318" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B319" s="2">
-        <v>45902.399930555555</v>
+        <v>45902.363310185188</v>
       </c>
       <c r="C319" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D319" s="4"/>
       <c r="E319" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F319" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B320" s="2">
-        <v>45902.399965277778</v>
+        <v>45902.363310185188</v>
       </c>
       <c r="C320" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D320" s="4"/>
       <c r="E320" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F320" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B321" s="2">
-        <v>46076.712152777778</v>
+        <v>45902.363310185188</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D321" s="4"/>
       <c r="E321" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F321" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B322" s="2">
-        <v>45902.365613425929</v>
+        <v>45902.363310185188</v>
       </c>
       <c r="C322" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D322" s="4"/>
       <c r="E322" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F322" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B323" s="2">
-        <v>45902.363807870373</v>
+        <v>45902.363310185188</v>
       </c>
       <c r="C323" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D323" s="4"/>
       <c r="E323" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F323" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B324" s="2">
-        <v>45902.363819444443</v>
+        <v>45902.363310185188</v>
       </c>
       <c r="C324" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D324" s="4"/>
       <c r="E324" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F324" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B325" s="2">
-        <v>45902.363888888889</v>
+        <v>45902.363310185188</v>
       </c>
       <c r="C325" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D325" s="4"/>
       <c r="E325" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F325" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B326" s="2">
-        <v>45902.363935185182</v>
+        <v>45902.363310185188</v>
       </c>
       <c r="C326" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D326" s="4"/>
       <c r="E326" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F326" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B327" s="2">
-        <v>45902.364166666666</v>
+        <v>46304.677488425928</v>
       </c>
       <c r="C327" s="3" t="s">
         <v>6</v>
@@ -8062,15 +8245,15 @@
         <v>10</v>
       </c>
       <c r="F327" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B328" s="2">
-        <v>45902.36791666667</v>
+        <v>46304.677499999998</v>
       </c>
       <c r="C328" s="3" t="s">
         <v>6</v>
@@ -8080,15 +8263,15 @@
         <v>10</v>
       </c>
       <c r="F328" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B329" s="2">
-        <v>45902.364247685182</v>
+        <v>46304.677499999998</v>
       </c>
       <c r="C329" s="3" t="s">
         <v>6</v>
@@ -8098,343 +8281,1673 @@
         <v>10</v>
       </c>
       <c r="F329" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A330" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B330" s="2">
+        <v>45902.363333333335</v>
+      </c>
+      <c r="C330" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D330" s="4"/>
+      <c r="E330" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F330" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A331" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B331" s="2">
+        <v>46304.677372685182</v>
+      </c>
+      <c r="C331" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D331" s="4"/>
+      <c r="E331" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F331" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A332" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B332" s="2">
+        <v>46304.677361111113</v>
+      </c>
+      <c r="C332" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D332" s="4"/>
+      <c r="E332" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F332" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A333" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B333" s="2">
+        <v>46304.677372685182</v>
+      </c>
+      <c r="C333" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D333" s="4"/>
+      <c r="E333" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F333" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A334" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B334" s="2">
+        <v>46304.677384259259</v>
+      </c>
+      <c r="C334" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D334" s="4"/>
+      <c r="E334" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F334" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A335" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B335" s="2">
+        <v>46304.677395833336</v>
+      </c>
+      <c r="C335" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D335" s="4"/>
+      <c r="E335" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F335" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A336" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B336" s="2">
+        <v>46304.677407407406</v>
+      </c>
+      <c r="C336" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D336" s="4"/>
+      <c r="E336" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F336" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A337" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B337" s="2">
+        <v>46304.677418981482</v>
+      </c>
+      <c r="C337" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D337" s="4"/>
+      <c r="E337" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F337" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A338" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B338" s="2">
+        <v>46304.677418981482</v>
+      </c>
+      <c r="C338" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D338" s="4"/>
+      <c r="E338" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F338" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A339" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B339" s="2">
+        <v>46304.677430555559</v>
+      </c>
+      <c r="C339" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D339" s="4"/>
+      <c r="E339" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F339" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A340" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B340" s="2">
+        <v>46304.677430555559</v>
+      </c>
+      <c r="C340" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D340" s="4"/>
+      <c r="E340" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F340" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A341" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B341" s="2">
+        <v>46304.677442129629</v>
+      </c>
+      <c r="C341" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D341" s="4"/>
+      <c r="E341" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F341" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A342" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B342" s="2">
+        <v>45902.399837962963</v>
+      </c>
+      <c r="C342" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D342" s="4"/>
+      <c r="E342" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F342" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A343" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B343" s="2">
+        <v>45902.363333333335</v>
+      </c>
+      <c r="C343" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D343" s="4"/>
+      <c r="E343" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F343" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A344" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B344" s="2">
+        <v>46304.677453703705</v>
+      </c>
+      <c r="C344" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D344" s="4"/>
+      <c r="E344" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F344" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A345" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B345" s="2">
+        <v>45902.363333333335</v>
+      </c>
+      <c r="C345" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D345" s="4"/>
+      <c r="E345" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F345" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A346" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B346" s="2">
+        <v>46304.677453703705</v>
+      </c>
+      <c r="C346" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D346" s="4"/>
+      <c r="E346" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F346" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A347" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B347" s="2">
+        <v>45902.363333333335</v>
+      </c>
+      <c r="C347" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D347" s="4"/>
+      <c r="E347" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F347" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A348" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B348" s="2">
+        <v>46304.677465277775</v>
+      </c>
+      <c r="C348" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D348" s="4"/>
+      <c r="E348" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F348" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A349" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B349" s="2">
+        <v>45902.363333333335</v>
+      </c>
+      <c r="C349" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D349" s="4"/>
+      <c r="E349" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F349" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A350" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B350" s="2">
+        <v>46304.677465277775</v>
+      </c>
+      <c r="C350" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D350" s="4"/>
+      <c r="E350" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F350" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A351" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B351" s="2">
+        <v>45902.363333333335</v>
+      </c>
+      <c r="C351" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D351" s="4"/>
+      <c r="E351" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F351" s="4" t="s">
         <v>123</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A352" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B352" s="2">
+        <v>46304.677476851852</v>
+      </c>
+      <c r="C352" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D352" s="4"/>
+      <c r="E352" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F352" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A353" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B353" s="2">
+        <v>45902.363333333335</v>
+      </c>
+      <c r="C353" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D353" s="4"/>
+      <c r="E353" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F353" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A354" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B354" s="2">
+        <v>46304.677488425928</v>
+      </c>
+      <c r="C354" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D354" s="4"/>
+      <c r="E354" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F354" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A355" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B355" s="2">
+        <v>46304.677488425928</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D355" s="4"/>
+      <c r="E355" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F355" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A356" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B356" s="2">
+        <v>45902.399918981479</v>
+      </c>
+      <c r="C356" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D356" s="4"/>
+      <c r="E356" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F356" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A357" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B357" s="2">
+        <v>45902.399930555555</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D357" s="4"/>
+      <c r="E357" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F357" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A358" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B358" s="2">
+        <v>45902.399965277778</v>
+      </c>
+      <c r="C358" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D358" s="4"/>
+      <c r="E358" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F358" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A359" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B359" s="2">
+        <v>46076.712152777778</v>
+      </c>
+      <c r="C359" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D359" s="4"/>
+      <c r="E359" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F359" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A360" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B360" s="2">
+        <v>46304.677499999998</v>
+      </c>
+      <c r="C360" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D360" s="4"/>
+      <c r="E360" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F360" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A361" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B361" s="2">
+        <v>46304.677499999998</v>
+      </c>
+      <c r="C361" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D361" s="4"/>
+      <c r="E361" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F361" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A362" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B362" s="2">
+        <v>46304.677499999998</v>
+      </c>
+      <c r="C362" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D362" s="4"/>
+      <c r="E362" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F362" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A363" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B363" s="2">
+        <v>46304.67763888889</v>
+      </c>
+      <c r="C363" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D363" s="4"/>
+      <c r="E363" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F363" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A364" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B364" s="2">
+        <v>46304.67763888889</v>
+      </c>
+      <c r="C364" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D364" s="4"/>
+      <c r="E364" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F364" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A365" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B365" s="2">
+        <v>46304.677881944444</v>
+      </c>
+      <c r="C365" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D365" s="4"/>
+      <c r="E365" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F365" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A366" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B366" s="2">
+        <v>46304.677916666667</v>
+      </c>
+      <c r="C366" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D366" s="4"/>
+      <c r="E366" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F366" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A367" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B367" s="2">
+        <v>46304.677499999998</v>
+      </c>
+      <c r="C367" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D367" s="4"/>
+      <c r="E367" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F367" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A368" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B368" s="2">
+        <v>46304.677627314813</v>
+      </c>
+      <c r="C368" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D368" s="4"/>
+      <c r="E368" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F368" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A369" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B369" s="2">
+        <v>46304.677881944444</v>
+      </c>
+      <c r="C369" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D369" s="4"/>
+      <c r="E369" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F369" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A370" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B370" s="2">
+        <v>46304.677881944444</v>
+      </c>
+      <c r="C370" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D370" s="4"/>
+      <c r="E370" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F370" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A371" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B371" s="2">
+        <v>46304.677893518521</v>
+      </c>
+      <c r="C371" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D371" s="4"/>
+      <c r="E371" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F371" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A372" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B372" s="2">
+        <v>46304.677893518521</v>
+      </c>
+      <c r="C372" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D372" s="4"/>
+      <c r="E372" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F372" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A373" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B373" s="2">
+        <v>46304.677893518521</v>
+      </c>
+      <c r="C373" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D373" s="4"/>
+      <c r="E373" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F373" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A374" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B374" s="2">
+        <v>46304.677916666667</v>
+      </c>
+      <c r="C374" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D374" s="4"/>
+      <c r="E374" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F374" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A375" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B375" s="2">
+        <v>45902.365613425929</v>
+      </c>
+      <c r="C375" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D375" s="4"/>
+      <c r="E375" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F375" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A376" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B376" s="2">
+        <v>45902.363807870373</v>
+      </c>
+      <c r="C376" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D376" s="4"/>
+      <c r="E376" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F376" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A377" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B377" s="2">
+        <v>45902.363819444443</v>
+      </c>
+      <c r="C377" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D377" s="4"/>
+      <c r="E377" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F377" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A378" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B378" s="2">
+        <v>45902.363888888889</v>
+      </c>
+      <c r="C378" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D378" s="4"/>
+      <c r="E378" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F378" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A379" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B379" s="2">
+        <v>45902.363935185182</v>
+      </c>
+      <c r="C379" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D379" s="4"/>
+      <c r="E379" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F379" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A380" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B380" s="2">
+        <v>45902.364166666666</v>
+      </c>
+      <c r="C380" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D380" s="4"/>
+      <c r="E380" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F380" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A381" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B381" s="2">
+        <v>45902.36791666667</v>
+      </c>
+      <c r="C381" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D381" s="4"/>
+      <c r="E381" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F381" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A382" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B382" s="2">
+        <v>45902.364247685182</v>
+      </c>
+      <c r="C382" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D382" s="4"/>
+      <c r="E382" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F382" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A383" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B383" s="2">
+        <v>46304.677939814814</v>
+      </c>
+      <c r="C383" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D383" s="4"/>
+      <c r="E383" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F383" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A384" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B384" s="2">
+        <v>46304.678344907406</v>
+      </c>
+      <c r="C384" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D384" s="4"/>
+      <c r="E384" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F384" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A385" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B385" s="2">
+        <v>46304.677939814814</v>
+      </c>
+      <c r="C385" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D385" s="4"/>
+      <c r="E385" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F385" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A386" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B386" s="2">
+        <v>46304.677928240744</v>
+      </c>
+      <c r="C386" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D386" s="4"/>
+      <c r="E386" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F386" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A387" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B387" s="2">
+        <v>46304.677928240744</v>
+      </c>
+      <c r="C387" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D387" s="4"/>
+      <c r="E387" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F387" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A388" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B388" s="2">
+        <v>46304.677928240744</v>
+      </c>
+      <c r="C388" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D388" s="4"/>
+      <c r="E388" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F388" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A389" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B389" s="2">
+        <v>46304.677939814814</v>
+      </c>
+      <c r="C389" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D389" s="4"/>
+      <c r="E389" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F389" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A390" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B390" s="2">
+        <v>46304.677939814814</v>
+      </c>
+      <c r="C390" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D390" s="4"/>
+      <c r="E390" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F390" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A391" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B391" s="2">
+        <v>46304.677939814814</v>
+      </c>
+      <c r="C391" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D391" s="4"/>
+      <c r="E391" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F391" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A392" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B392" s="2">
+        <v>46304.677939814814</v>
+      </c>
+      <c r="C392" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D392" s="4"/>
+      <c r="E392" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F392" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A393" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B393" s="2">
+        <v>46304.677951388891</v>
+      </c>
+      <c r="C393" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D393" s="4"/>
+      <c r="E393" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F393" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A394" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B394" s="2">
+        <v>46304.67796296296</v>
+      </c>
+      <c r="C394" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D394" s="4"/>
+      <c r="E394" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F394" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A395" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B395" s="2">
+        <v>46304.677974537037</v>
+      </c>
+      <c r="C395" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D395" s="4"/>
+      <c r="E395" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F395" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A396" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B396" s="2">
+        <v>46304.677986111114</v>
+      </c>
+      <c r="C396" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D396" s="4"/>
+      <c r="E396" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F396" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A397" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B397" s="2">
+        <v>46304.678020833337</v>
+      </c>
+      <c r="C397" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D397" s="4"/>
+      <c r="E397" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F397" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A398" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B398" s="2">
+        <v>46304.678124999999</v>
+      </c>
+      <c r="C398" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D398" s="4"/>
+      <c r="E398" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F398" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A399" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B399" s="2">
+        <v>46304.678344907406</v>
+      </c>
+      <c r="C399" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D399" s="4"/>
+      <c r="E399" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F399" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{6BEDDAB4-8B47-445A-A8B9-FC5A39C08E5E}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{5BA57792-E79B-45B0-95F1-E1568D72D281}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{4C330DD7-5E55-4BA9-B92F-DB0BE2E9FF96}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{7F63FB80-F661-43E4-8145-7210D5336B2D}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{9B6812C5-7CFE-4FA4-8C92-ADA90758503E}"/>
-    <hyperlink ref="A7" r:id="rId6" xr:uid="{5916D0D6-65E6-488C-BB43-A62AC9E1D7C0}"/>
-    <hyperlink ref="A8" r:id="rId7" xr:uid="{5B90A81E-E3D8-4C9B-9C99-314C224D10E9}"/>
-    <hyperlink ref="A9" r:id="rId8" xr:uid="{E5A89B17-872A-4039-BDAA-FA27CEA5353E}"/>
-    <hyperlink ref="A10" r:id="rId9" xr:uid="{778B1B47-4DE4-4520-90C1-BA37D610FF9D}"/>
-    <hyperlink ref="A11" r:id="rId10" xr:uid="{382535C2-DEAA-49DB-9C76-D1C267B3AC8B}"/>
-    <hyperlink ref="A12" r:id="rId11" xr:uid="{56D7F8D1-B0CD-4CA6-AA92-318DCE32D0F7}"/>
-    <hyperlink ref="A13" r:id="rId12" xr:uid="{6629BF47-7183-4881-852F-5889F83CFE94}"/>
-    <hyperlink ref="A14" r:id="rId13" xr:uid="{04C0CE4F-C7F9-4031-A7CA-4E60BB8D053A}"/>
-    <hyperlink ref="A15" r:id="rId14" xr:uid="{10FD8AE4-C395-4126-933D-50E21B22ADF7}"/>
-    <hyperlink ref="A16" r:id="rId15" xr:uid="{3BE75D44-57F8-44E2-8228-0C6B831CF06E}"/>
-    <hyperlink ref="A17" r:id="rId16" xr:uid="{561FE289-7075-4CCC-AB3A-7EA48AE47007}"/>
-    <hyperlink ref="A18" r:id="rId17" xr:uid="{8D36EEA2-4195-4D26-90B3-22EAD1C717DF}"/>
-    <hyperlink ref="A19" r:id="rId18" xr:uid="{B07D435E-2ED5-4BB0-89E1-BDD45F47E99A}"/>
-    <hyperlink ref="A20" r:id="rId19" xr:uid="{78BA0F79-0F6F-46AA-83FC-BC913C8D826E}"/>
-    <hyperlink ref="A21" r:id="rId20" xr:uid="{2767A34E-6403-4966-82D7-2419380E4009}"/>
-    <hyperlink ref="A22" r:id="rId21" xr:uid="{C52D864B-85AE-46FD-9A75-EA455F661A6A}"/>
-    <hyperlink ref="A23" r:id="rId22" xr:uid="{8B2BD559-8EC6-4136-8DDD-5DB797048811}"/>
-    <hyperlink ref="A24" r:id="rId23" xr:uid="{9A3FD176-E7F6-4C56-887A-3972AD4CFC0D}"/>
-    <hyperlink ref="A25" r:id="rId24" xr:uid="{03DE51BC-664B-4422-A8C5-8F932E3350DC}"/>
-    <hyperlink ref="A26" r:id="rId25" xr:uid="{485FFC3A-B52E-4106-93F3-5DCEA3FF0EE7}"/>
-    <hyperlink ref="A27" r:id="rId26" xr:uid="{9BFC90DE-060D-4AA0-9F05-875E8D27949E}"/>
-    <hyperlink ref="A28" r:id="rId27" xr:uid="{C9646895-0F18-4145-AE9D-5C8E6D122300}"/>
-    <hyperlink ref="A29" r:id="rId28" xr:uid="{F4491D36-FF70-4E55-AE0C-99EC797489D0}"/>
-    <hyperlink ref="A30" r:id="rId29" xr:uid="{1F38AB45-C1A1-41E4-B54C-79E942FCAEF9}"/>
-    <hyperlink ref="A31" r:id="rId30" xr:uid="{388DA1DA-A723-4BE3-A7FD-E87E1D5ADA78}"/>
-    <hyperlink ref="A32" r:id="rId31" xr:uid="{F23EAE7A-104F-4ED8-B472-5B30CE4849B3}"/>
-    <hyperlink ref="A33" r:id="rId32" xr:uid="{4DD33C92-8A49-4457-AD7D-F0C9AA05D63A}"/>
-    <hyperlink ref="A34" r:id="rId33" xr:uid="{77B0EBE5-F9F5-4DCF-AE6D-410549F77C9B}"/>
-    <hyperlink ref="A35" r:id="rId34" xr:uid="{391E5BE2-3366-4286-9C19-B91F63B7BA68}"/>
-    <hyperlink ref="A36" r:id="rId35" xr:uid="{6E91D26B-105F-4591-9B17-9A6B2341C909}"/>
-    <hyperlink ref="A37" r:id="rId36" xr:uid="{9F853882-BD08-4546-AD8E-C802812B9385}"/>
-    <hyperlink ref="A38" r:id="rId37" xr:uid="{208BE7AD-11A1-43D9-B090-0B766A6E636F}"/>
-    <hyperlink ref="A39" r:id="rId38" xr:uid="{CF3EC7BA-CAB9-40F2-9A36-2895F252AF9E}"/>
-    <hyperlink ref="A40" r:id="rId39" xr:uid="{7F7D089D-00DE-4E5F-8E36-6D9EF3032732}"/>
-    <hyperlink ref="A41" r:id="rId40" xr:uid="{8E0E3FCC-8213-4524-B5B8-CAE96DA2A1D9}"/>
-    <hyperlink ref="A42" r:id="rId41" xr:uid="{D9017721-AA0C-47AC-9DC6-7581F607C342}"/>
-    <hyperlink ref="A43" r:id="rId42" xr:uid="{54E33EBA-1AF6-4BFB-8806-2A55F7CCAE3E}"/>
-    <hyperlink ref="A44" r:id="rId43" xr:uid="{83730F9A-9338-4E13-B792-7DEE404D310A}"/>
-    <hyperlink ref="A45" r:id="rId44" xr:uid="{CDBFD360-6DB5-4404-85EF-E3C4412786BB}"/>
-    <hyperlink ref="A46" r:id="rId45" xr:uid="{A8A8126B-5D06-4313-A038-80B01FB3A32D}"/>
-    <hyperlink ref="A47" r:id="rId46" xr:uid="{D10009C3-5091-4A31-90D0-E7C3AADAA291}"/>
-    <hyperlink ref="A48" r:id="rId47" xr:uid="{AA5A2C80-62E8-4FB4-8997-836F9B149BC2}"/>
-    <hyperlink ref="A49" r:id="rId48" xr:uid="{DE12A3F4-0BE8-4252-8F4F-B59DCD3AEE14}"/>
-    <hyperlink ref="A50" r:id="rId49" xr:uid="{F912AE9A-1F7D-447B-A93A-E154131B3774}"/>
-    <hyperlink ref="A51" r:id="rId50" xr:uid="{CCA2947B-AF96-4ADB-A1C8-75F95727BA9E}"/>
-    <hyperlink ref="A52" r:id="rId51" xr:uid="{887B3DE4-BB71-4BB6-A6CA-39E2CE997D83}"/>
-    <hyperlink ref="A53" r:id="rId52" xr:uid="{E06A0151-920E-466C-98D2-D098E5BE1089}"/>
-    <hyperlink ref="A54" r:id="rId53" xr:uid="{D6EBBEE0-2C3F-4EB5-BA7F-A21EDF1AA741}"/>
-    <hyperlink ref="A55" r:id="rId54" xr:uid="{444C5E36-AE5C-4CE0-B79A-F0CBF9D7B9D4}"/>
-    <hyperlink ref="A56" r:id="rId55" xr:uid="{0450D083-0F9A-48C1-8D96-B0EE93D38C2F}"/>
-    <hyperlink ref="A57" r:id="rId56" xr:uid="{C73E02D7-5B2F-44B7-9380-9FD4C933B268}"/>
-    <hyperlink ref="A58" r:id="rId57" xr:uid="{4A6E0012-1DFD-4B8B-A5C6-9CCDBAC728FC}"/>
-    <hyperlink ref="A59" r:id="rId58" xr:uid="{1A4DBC3F-B2E1-4F31-8FC1-63A85FC1EA92}"/>
-    <hyperlink ref="A60" r:id="rId59" xr:uid="{DC535C12-A742-4117-938B-474243C130D9}"/>
-    <hyperlink ref="A61" r:id="rId60" xr:uid="{024C2712-1230-4F82-B426-2F581D6DEB2B}"/>
-    <hyperlink ref="A62" r:id="rId61" xr:uid="{125D4FDE-0F9D-441E-A0B0-9A832400E31E}"/>
-    <hyperlink ref="A63" r:id="rId62" xr:uid="{56A1F09D-F540-496F-9F25-91EC0C025CF0}"/>
-    <hyperlink ref="A64" r:id="rId63" xr:uid="{68E11941-8291-4F1F-9827-37DD63D93C9B}"/>
-    <hyperlink ref="A65" r:id="rId64" xr:uid="{00ACE526-72B7-4666-88DE-FCBB1219525C}"/>
-    <hyperlink ref="A66" r:id="rId65" xr:uid="{E0D9C6E0-BBE3-493C-BEF6-7E68F6699776}"/>
-    <hyperlink ref="A67" r:id="rId66" xr:uid="{E8CC6415-8E14-456D-9E21-014DA989FF95}"/>
-    <hyperlink ref="A68" r:id="rId67" xr:uid="{CFC6DEE9-3958-4758-AB9B-14C4482F62A5}"/>
-    <hyperlink ref="A69" r:id="rId68" xr:uid="{75E7BFAE-F81D-4F4F-9E7A-2A164D534AC0}"/>
-    <hyperlink ref="A70" r:id="rId69" xr:uid="{D30DBD44-E0DE-42DA-8880-10C27A7A466B}"/>
-    <hyperlink ref="A71" r:id="rId70" xr:uid="{75B4D128-5BA9-4F25-A14C-3FA005138D00}"/>
-    <hyperlink ref="A72" r:id="rId71" xr:uid="{6026DAAB-EB0D-4C2C-B8F2-25E310F1983A}"/>
-    <hyperlink ref="A73" r:id="rId72" xr:uid="{CF7F5B95-59E3-425C-839A-756E13460D0B}"/>
-    <hyperlink ref="A74" r:id="rId73" xr:uid="{5795971B-8107-4A79-A465-0F6B24CF4999}"/>
-    <hyperlink ref="A75" r:id="rId74" xr:uid="{A9401496-DE2F-4F94-955E-1515B8F0BA98}"/>
-    <hyperlink ref="A76" r:id="rId75" xr:uid="{D8B7B719-F7FC-4D2D-80FB-25706738DAFD}"/>
-    <hyperlink ref="A77" r:id="rId76" xr:uid="{1EFE9AEB-5F3B-40A5-8136-A09FB73624FB}"/>
-    <hyperlink ref="A78" r:id="rId77" xr:uid="{C8E0F43A-1CAC-4AA9-8EF6-EF445159963F}"/>
-    <hyperlink ref="A79" r:id="rId78" xr:uid="{12E0AB85-1120-4584-A084-FBE64B5FAEAA}"/>
-    <hyperlink ref="A80" r:id="rId79" xr:uid="{71C156A5-DA43-4C06-849F-67E20EC2C569}"/>
-    <hyperlink ref="A81" r:id="rId80" xr:uid="{916BBB47-E113-4AD6-A72B-AB8C2148AD26}"/>
-    <hyperlink ref="A82" r:id="rId81" xr:uid="{7F829739-252B-4CDF-A626-44C1085AC96F}"/>
-    <hyperlink ref="A83" r:id="rId82" xr:uid="{01DFE17F-54AF-4748-9F98-C73AB6C7EBB4}"/>
-    <hyperlink ref="A84" r:id="rId83" xr:uid="{BB12C5EF-9A99-4F30-9E8B-2FAF8775A6D8}"/>
-    <hyperlink ref="A85" r:id="rId84" xr:uid="{3185CA89-4C59-4880-82E5-4154C09EBF47}"/>
-    <hyperlink ref="A86" r:id="rId85" xr:uid="{FCB17CA0-6403-4E67-BE64-CFC047270F99}"/>
-    <hyperlink ref="A87" r:id="rId86" xr:uid="{A1A32E63-CD49-43D4-8555-63B9B71B2E10}"/>
-    <hyperlink ref="A88" r:id="rId87" xr:uid="{573C7A40-C74C-4B43-A6C7-F1468CFB29F7}"/>
-    <hyperlink ref="A89" r:id="rId88" xr:uid="{EB357E8F-0A2C-4863-83E0-1DCC8D06B899}"/>
-    <hyperlink ref="A90" r:id="rId89" xr:uid="{A0ED17D8-1C91-4172-9E0B-90FB3AF94C93}"/>
-    <hyperlink ref="A91" r:id="rId90" xr:uid="{D89202AA-4CA3-4498-9348-CB5E25FB3960}"/>
-    <hyperlink ref="A92" r:id="rId91" xr:uid="{05D54FAD-C2D4-459E-ABB9-1762E3143B30}"/>
-    <hyperlink ref="A93" r:id="rId92" xr:uid="{35A042BA-64E7-4CA8-8BF1-66E64662DE76}"/>
-    <hyperlink ref="A94" r:id="rId93" xr:uid="{845CC79F-74C9-4E24-B3CF-1CFD675EE5BF}"/>
-    <hyperlink ref="A95" r:id="rId94" xr:uid="{909392D9-F54E-4F8E-88B6-656FA37E54DA}"/>
-    <hyperlink ref="A96" r:id="rId95" xr:uid="{894543FA-5001-4195-9196-B3B5D105D391}"/>
-    <hyperlink ref="A97" r:id="rId96" xr:uid="{7031F5A1-A5E5-4930-AFFC-8031CFCFD78A}"/>
-    <hyperlink ref="A98" r:id="rId97" xr:uid="{917ABA1E-81B1-4189-9023-DEFFE1C2866A}"/>
-    <hyperlink ref="A99" r:id="rId98" xr:uid="{AC96113D-B825-4A1A-9AA0-104283FB2B85}"/>
-    <hyperlink ref="A100" r:id="rId99" xr:uid="{0E8633B7-2F9A-443C-96DA-BB37B793AFFB}"/>
-    <hyperlink ref="A101" r:id="rId100" xr:uid="{755696F5-4285-4F30-A3A4-6C0CFD189C33}"/>
-    <hyperlink ref="A102" r:id="rId101" xr:uid="{3265BE42-AFAD-4645-B1BD-7B2F531E6D04}"/>
-    <hyperlink ref="A103" r:id="rId102" xr:uid="{8CF778AB-5A94-4313-A5FF-9405B230A027}"/>
-    <hyperlink ref="A104" r:id="rId103" xr:uid="{B860DF64-AC9F-437C-8112-58E889C36FAD}"/>
-    <hyperlink ref="A105" r:id="rId104" xr:uid="{1CD4F63F-6847-420E-8655-DD4BCC0D7155}"/>
-    <hyperlink ref="A106" r:id="rId105" xr:uid="{B2EF437B-2A5C-425A-9BEC-F738FD4DBAEA}"/>
-    <hyperlink ref="A107" r:id="rId106" xr:uid="{CED7A64B-1450-4F1A-82EE-68981C931CDA}"/>
-    <hyperlink ref="A108" r:id="rId107" xr:uid="{C5708382-1FAF-4CD9-AB3B-3AA1596B1F5D}"/>
-    <hyperlink ref="A109" r:id="rId108" xr:uid="{F521F4E1-7B93-4CBF-B2DB-6A88B2AA9D82}"/>
-    <hyperlink ref="A110" r:id="rId109" xr:uid="{678B1A87-A584-4CE5-AEC0-33A1B41D7B19}"/>
-    <hyperlink ref="A111" r:id="rId110" xr:uid="{E3275E1A-02DC-4AB1-99A3-2D661F30A157}"/>
-    <hyperlink ref="A112" r:id="rId111" xr:uid="{8C650242-2295-49D9-83F3-083FCEDF5FDE}"/>
-    <hyperlink ref="A113" r:id="rId112" xr:uid="{56B9E4D9-5CCA-4F1E-BB76-CCECD9EE27C2}"/>
-    <hyperlink ref="A114" r:id="rId113" xr:uid="{35B71CB9-A79D-4697-8AA8-D04A21FBD561}"/>
-    <hyperlink ref="A115" r:id="rId114" xr:uid="{575FCEF8-B8FC-4B41-BFE4-AE59BBF7C351}"/>
-    <hyperlink ref="A116" r:id="rId115" xr:uid="{F0502F32-5510-4CC1-8875-3E7AD65EE8F6}"/>
-    <hyperlink ref="A117" r:id="rId116" xr:uid="{5B6ED225-66DE-45EC-A74D-44419F4C66FF}"/>
-    <hyperlink ref="A118" r:id="rId117" xr:uid="{82869B38-98E3-40DA-A272-FF75A2BF7A73}"/>
-    <hyperlink ref="A119" r:id="rId118" xr:uid="{BA3D71B0-10AC-4217-8081-6F4689C21563}"/>
-    <hyperlink ref="A120" r:id="rId119" xr:uid="{CEB5D1B1-FD37-4A0B-8542-99F2DA6A29A8}"/>
-    <hyperlink ref="A121" r:id="rId120" xr:uid="{2040FA31-D970-4B62-86B4-270A0774A50D}"/>
-    <hyperlink ref="A122" r:id="rId121" xr:uid="{2530C92C-B460-4C0A-ADD9-3A10DE284F34}"/>
-    <hyperlink ref="A123" r:id="rId122" xr:uid="{AC354E96-AA84-4F9B-898E-297F621164C7}"/>
-    <hyperlink ref="A124" r:id="rId123" xr:uid="{270C290F-29F2-4AD5-8CF8-EA55C705E440}"/>
-    <hyperlink ref="A125" r:id="rId124" xr:uid="{3528ADBA-9427-4A8A-8F1A-7C87DD5E601D}"/>
-    <hyperlink ref="A126" r:id="rId125" xr:uid="{FC03C7EC-8932-4A42-839B-7DEB1F7D5B83}"/>
-    <hyperlink ref="A127" r:id="rId126" xr:uid="{90BC390A-AC2D-48DB-A3C0-D3DEAAE1FFA8}"/>
-    <hyperlink ref="A128" r:id="rId127" xr:uid="{6096177B-80C9-4E8C-B29F-95DDE24AEA05}"/>
-    <hyperlink ref="A129" r:id="rId128" xr:uid="{3AB6ACC9-5A8B-4902-9D64-8814D63A59C6}"/>
-    <hyperlink ref="A130" r:id="rId129" xr:uid="{146A5FEA-CEB7-4A66-9358-1FAF36E5362C}"/>
-    <hyperlink ref="A131" r:id="rId130" xr:uid="{F9E81788-535E-4982-AF9A-AECF0ED3FB65}"/>
-    <hyperlink ref="A132" r:id="rId131" xr:uid="{B86500E6-7157-4B53-8871-A24DE800CF36}"/>
-    <hyperlink ref="A133" r:id="rId132" xr:uid="{6732D560-8AAC-4247-AA3E-57E0F4BE184B}"/>
-    <hyperlink ref="A134" r:id="rId133" xr:uid="{5D42EAF1-59C2-4DFC-9E0D-06EB10BE3FB6}"/>
-    <hyperlink ref="A135" r:id="rId134" xr:uid="{DD1321B8-04AB-474C-9F65-80607D09C6BE}"/>
-    <hyperlink ref="A136" r:id="rId135" xr:uid="{7BF14750-4FA1-452B-A219-13A676B77A61}"/>
-    <hyperlink ref="A137" r:id="rId136" xr:uid="{DAE7258E-6A38-4D98-9056-390D290D839C}"/>
-    <hyperlink ref="A138" r:id="rId137" xr:uid="{5C692AE5-9F8C-484B-8865-015F70B20DB5}"/>
-    <hyperlink ref="A139" r:id="rId138" xr:uid="{E13A23BE-CFD1-459E-9E56-05429027FE4D}"/>
-    <hyperlink ref="A140" r:id="rId139" xr:uid="{104B618C-051F-4C12-A186-6F967DDCF6C3}"/>
-    <hyperlink ref="A141" r:id="rId140" xr:uid="{AC54B66E-4565-471F-980A-5A84AB536050}"/>
-    <hyperlink ref="A142" r:id="rId141" xr:uid="{51101F41-816D-465F-AAD1-BC791F536F39}"/>
-    <hyperlink ref="A143" r:id="rId142" xr:uid="{A7FFE6EE-790C-457D-B804-C628D0C8ADB3}"/>
-    <hyperlink ref="A144" r:id="rId143" xr:uid="{7C98E0C7-62CC-4043-B053-90B6B43D7537}"/>
-    <hyperlink ref="A145" r:id="rId144" xr:uid="{2B2E6FDB-B305-4121-A8A3-5150BA05401F}"/>
-    <hyperlink ref="A146" r:id="rId145" xr:uid="{FBD993DA-E535-415D-AC49-A9ED249F8EA3}"/>
-    <hyperlink ref="A147" r:id="rId146" xr:uid="{BDA2597E-4DB1-4D90-BDD6-6948C904BD57}"/>
-    <hyperlink ref="A148" r:id="rId147" xr:uid="{4EBA1D66-8757-4390-8EB9-B7127136F1AA}"/>
-    <hyperlink ref="A149" r:id="rId148" xr:uid="{65B36521-BB6F-48B6-BC4A-D7EA433BC748}"/>
-    <hyperlink ref="A150" r:id="rId149" xr:uid="{8F0FA97B-05B3-4C94-A635-53C348898ACD}"/>
-    <hyperlink ref="A151" r:id="rId150" xr:uid="{871AD796-A5E0-4DBF-A80C-CF19286A8706}"/>
-    <hyperlink ref="A152" r:id="rId151" xr:uid="{AC69A622-0762-457A-BEA1-B3371AA1166A}"/>
-    <hyperlink ref="A153" r:id="rId152" xr:uid="{0386B682-4C2D-471B-8518-ECB6ACFC4CDC}"/>
-    <hyperlink ref="A154" r:id="rId153" xr:uid="{EF457A72-F592-4B5E-A006-FD52E25B2044}"/>
-    <hyperlink ref="A155" r:id="rId154" xr:uid="{524A4225-9695-4F2A-99E0-AADA8E7DA40B}"/>
-    <hyperlink ref="A156" r:id="rId155" xr:uid="{BD851FE3-CF51-44CC-8AFF-549AC7CF2B37}"/>
-    <hyperlink ref="A157" r:id="rId156" xr:uid="{DC86BC12-CC8E-43A8-87CD-64F565776087}"/>
-    <hyperlink ref="A158" r:id="rId157" xr:uid="{18E35748-0927-46C1-BC38-D92E56B57729}"/>
-    <hyperlink ref="A159" r:id="rId158" xr:uid="{FE2C0B24-E071-4BF0-84D7-C7E822A32019}"/>
-    <hyperlink ref="A160" r:id="rId159" xr:uid="{84FD477F-3C76-4AD9-9174-2A00CCC58105}"/>
-    <hyperlink ref="A161" r:id="rId160" xr:uid="{9A5C9581-9657-48D4-A707-6EEDC5CB9971}"/>
-    <hyperlink ref="A162" r:id="rId161" xr:uid="{42A57234-404E-49C4-B938-F9AF3333A65A}"/>
-    <hyperlink ref="A163" r:id="rId162" xr:uid="{2EC67F30-94A3-4996-A3FD-9C06F85F3C39}"/>
-    <hyperlink ref="A164" r:id="rId163" xr:uid="{51E24EBE-7CD0-48A3-8818-1F3D649E1AB3}"/>
-    <hyperlink ref="A165" r:id="rId164" xr:uid="{3F0BA34A-DE10-4724-BA0B-6D85C58D1417}"/>
-    <hyperlink ref="A166" r:id="rId165" xr:uid="{A028012F-28AA-4296-99F2-3347A8485DD4}"/>
-    <hyperlink ref="A167" r:id="rId166" xr:uid="{88F11F95-D15F-48A6-B85D-CCAADBE251F9}"/>
-    <hyperlink ref="A168" r:id="rId167" xr:uid="{874F2CFF-972D-4F02-B0C6-94B34B67FD10}"/>
-    <hyperlink ref="A169" r:id="rId168" xr:uid="{967BCB72-4F7F-4DE6-9B37-824190274C04}"/>
-    <hyperlink ref="A170" r:id="rId169" xr:uid="{B349A517-DACF-4614-9D7C-FFE1A8FF1D6A}"/>
-    <hyperlink ref="A171" r:id="rId170" xr:uid="{AB304D0B-ED65-4643-9FC3-69939E026388}"/>
-    <hyperlink ref="A172" r:id="rId171" xr:uid="{78B9CE7E-AF16-4C88-8BBB-CA11871DC47E}"/>
-    <hyperlink ref="A173" r:id="rId172" xr:uid="{01464BD8-2B5C-4699-BC27-C8B45AEF380F}"/>
-    <hyperlink ref="A174" r:id="rId173" xr:uid="{07A28484-6939-4819-9F2F-D3AB8247E584}"/>
-    <hyperlink ref="A175" r:id="rId174" xr:uid="{2C091B91-BF75-46F4-BF6D-433586999281}"/>
-    <hyperlink ref="A176" r:id="rId175" xr:uid="{74FB5EBA-8509-45C0-93CF-8610E091D481}"/>
-    <hyperlink ref="A177" r:id="rId176" xr:uid="{AF1D134B-E342-4FAD-A554-EF75B22902D7}"/>
-    <hyperlink ref="A178" r:id="rId177" xr:uid="{8A80DDEB-200F-417A-B7F9-60B7A9C9F3F6}"/>
-    <hyperlink ref="A179" r:id="rId178" xr:uid="{5F8453C8-00EF-4CA0-8386-92D632EBEDA7}"/>
-    <hyperlink ref="A180" r:id="rId179" xr:uid="{055F46FC-5CE4-4896-8BB6-DEEECCDAC083}"/>
-    <hyperlink ref="A181" r:id="rId180" xr:uid="{C6238A5C-7459-4DFE-A004-7025DF9B1CFC}"/>
-    <hyperlink ref="A182" r:id="rId181" xr:uid="{3B0A64B5-44B3-4E7C-B39F-2FB813777B9F}"/>
-    <hyperlink ref="A183" r:id="rId182" xr:uid="{1357D648-B211-45FE-BD6C-88E64D824CE6}"/>
-    <hyperlink ref="A184" r:id="rId183" xr:uid="{2E3ED5EC-75D3-4A07-8137-64ED2369C357}"/>
-    <hyperlink ref="A185" r:id="rId184" xr:uid="{D737883C-E7D2-4129-866A-381E10B4378E}"/>
-    <hyperlink ref="A186" r:id="rId185" xr:uid="{14D98DD4-78C9-4A73-B896-22CA74D21647}"/>
-    <hyperlink ref="A187" r:id="rId186" xr:uid="{3516C147-821F-4405-AA92-F948B588483C}"/>
-    <hyperlink ref="A188" r:id="rId187" xr:uid="{24901C9A-3C68-43E2-9E8E-6823847F6834}"/>
-    <hyperlink ref="A189" r:id="rId188" xr:uid="{F46B7E59-1FEF-401A-B46B-E2C57EC881A4}"/>
-    <hyperlink ref="A190" r:id="rId189" xr:uid="{78965E48-9F5C-4E28-BCB0-18CDD4BEF8BE}"/>
-    <hyperlink ref="A191" r:id="rId190" xr:uid="{33F974B0-BD9B-4C75-97EE-BD3145A3DF62}"/>
-    <hyperlink ref="A192" r:id="rId191" xr:uid="{66A538FC-4C44-42B2-BF2B-C0BD3E766AC4}"/>
-    <hyperlink ref="A193" r:id="rId192" xr:uid="{D2A8AA45-3E22-4347-B8EB-C209C52DB8C8}"/>
-    <hyperlink ref="A194" r:id="rId193" xr:uid="{F17F9841-D58E-4468-86B1-8C9FE10F7025}"/>
-    <hyperlink ref="A195" r:id="rId194" xr:uid="{C0FCD583-23DD-4B11-947D-94ECE8456803}"/>
-    <hyperlink ref="A196" r:id="rId195" xr:uid="{68E5E3E3-4CD9-434F-BC65-6BB54552A2C1}"/>
-    <hyperlink ref="A197" r:id="rId196" xr:uid="{480A75A0-CC61-40DF-838B-F963DDCC4AFB}"/>
-    <hyperlink ref="A198" r:id="rId197" xr:uid="{1447F43B-B17B-497C-8F2B-9AB11C513C1A}"/>
-    <hyperlink ref="A199" r:id="rId198" xr:uid="{D995DDF9-5F91-4370-85BF-6E63E738CF11}"/>
-    <hyperlink ref="A200" r:id="rId199" xr:uid="{991BA74C-7589-47F3-861E-39C3594AAB24}"/>
-    <hyperlink ref="A201" r:id="rId200" xr:uid="{15BCE506-B20F-4884-ADF4-83C48BD9C863}"/>
-    <hyperlink ref="A202" r:id="rId201" xr:uid="{1949F5F7-36FD-42CE-8854-CF4C63A6F636}"/>
-    <hyperlink ref="A203" r:id="rId202" xr:uid="{AA4C9FFC-3FAD-478B-83B9-150115A00D3F}"/>
-    <hyperlink ref="A204" r:id="rId203" xr:uid="{61129A14-24CF-49F3-AFCF-F0B760A27CFD}"/>
-    <hyperlink ref="A205" r:id="rId204" xr:uid="{55B0E98C-5229-40EB-AC30-61E7ED3B9E0C}"/>
-    <hyperlink ref="A206" r:id="rId205" xr:uid="{7FE40326-0113-46AE-815B-F0C002A0FCB3}"/>
-    <hyperlink ref="A207" r:id="rId206" xr:uid="{629C9792-DFE9-4571-B7E4-4C9CDDC276A2}"/>
-    <hyperlink ref="A208" r:id="rId207" xr:uid="{5BD4FAFC-220D-4F8C-9777-315D7B5C0517}"/>
-    <hyperlink ref="A209" r:id="rId208" xr:uid="{A62143A1-ABCE-4400-8ED4-F678D4E1B9A5}"/>
-    <hyperlink ref="A210" r:id="rId209" xr:uid="{C378A378-196B-48B7-A82E-A480CDFDE792}"/>
-    <hyperlink ref="A211" r:id="rId210" xr:uid="{91F05FE0-3EE6-4EF1-BAB3-CE053963F297}"/>
-    <hyperlink ref="A212" r:id="rId211" xr:uid="{6FEE9A2F-DD3D-4B31-A191-A37440EBB021}"/>
-    <hyperlink ref="A213" r:id="rId212" xr:uid="{104E286E-2712-4827-A237-B2C408E94BB3}"/>
-    <hyperlink ref="A214" r:id="rId213" xr:uid="{E07A68C9-2B6C-4E63-8B6D-D5CB5DCF18BC}"/>
-    <hyperlink ref="A215" r:id="rId214" xr:uid="{0DAD701E-0F7D-48BD-B4A0-8470078F845A}"/>
-    <hyperlink ref="A216" r:id="rId215" xr:uid="{7C1D4D3F-9C8C-4B89-B81F-B8A3D1AB3711}"/>
-    <hyperlink ref="A217" r:id="rId216" xr:uid="{F64FE64F-F51C-488D-B60A-53786C5988EF}"/>
-    <hyperlink ref="A218" r:id="rId217" xr:uid="{600E94D0-7EE0-4829-87BD-42E2B1DE2E9C}"/>
-    <hyperlink ref="A219" r:id="rId218" xr:uid="{AD66FFDF-1077-4FD4-838C-2FA243E31FE3}"/>
-    <hyperlink ref="A220" r:id="rId219" xr:uid="{D84320A1-0479-456B-B7E0-94433B5298CC}"/>
-    <hyperlink ref="A221" r:id="rId220" xr:uid="{49FD8F31-228F-4F4A-BCDC-68DD9238BBB2}"/>
-    <hyperlink ref="A222" r:id="rId221" xr:uid="{DD6D671E-3611-4C6D-871E-C4C7E03750EC}"/>
-    <hyperlink ref="A223" r:id="rId222" xr:uid="{4C34839D-7AEF-4324-BF47-F00FF652858B}"/>
-    <hyperlink ref="A224" r:id="rId223" xr:uid="{3FDACD43-3AE0-4DAC-B101-F4111A23F716}"/>
-    <hyperlink ref="A225" r:id="rId224" xr:uid="{56197908-4E55-4711-BC30-9105E8620053}"/>
-    <hyperlink ref="A226" r:id="rId225" xr:uid="{6597A660-6427-4A6C-9D02-EAF1F1F262DC}"/>
-    <hyperlink ref="A227" r:id="rId226" xr:uid="{03136ACF-74FC-482F-96C0-98A2FED8CEBD}"/>
-    <hyperlink ref="A228" r:id="rId227" xr:uid="{A3DCC318-D577-4EC2-A3C1-C6DE4617C627}"/>
-    <hyperlink ref="A229" r:id="rId228" xr:uid="{88F4FCA6-1BFB-41BC-B730-2139E3A3AFD0}"/>
-    <hyperlink ref="A230" r:id="rId229" xr:uid="{2D96FB19-F2D2-4951-9C55-DF457860599E}"/>
-    <hyperlink ref="A231" r:id="rId230" xr:uid="{2BC11D98-6721-418D-AD17-58A96A88221D}"/>
-    <hyperlink ref="A232" r:id="rId231" xr:uid="{5F991CCB-5566-499B-A059-B96AE4832EBA}"/>
-    <hyperlink ref="A233" r:id="rId232" xr:uid="{DE53124D-29DD-4742-B107-0F4504303F90}"/>
-    <hyperlink ref="A234" r:id="rId233" xr:uid="{67D442BC-28A2-46AE-A271-CEB9B8ADEBAB}"/>
-    <hyperlink ref="A235" r:id="rId234" xr:uid="{47943595-5924-49E7-BF23-CCDDE763E07D}"/>
-    <hyperlink ref="A236" r:id="rId235" xr:uid="{E8590D27-54A2-42BE-94FB-050951B5DF5B}"/>
-    <hyperlink ref="A237" r:id="rId236" xr:uid="{CF95D15D-8D19-487A-A683-A1B51E890493}"/>
-    <hyperlink ref="A238" r:id="rId237" xr:uid="{92441F72-3006-4A94-8794-AE25122B37C5}"/>
-    <hyperlink ref="A239" r:id="rId238" xr:uid="{085521A7-F041-4CBE-A5F7-D35EF37EFAF5}"/>
-    <hyperlink ref="A240" r:id="rId239" xr:uid="{D8FB8C08-B7FC-4C79-A650-0C6CE82B4EE3}"/>
-    <hyperlink ref="A241" r:id="rId240" xr:uid="{092A215D-01E0-4CDD-8D67-CD0393A962A1}"/>
-    <hyperlink ref="A242" r:id="rId241" xr:uid="{3FD22F34-B564-4EDB-91F5-53D3564F5C72}"/>
-    <hyperlink ref="A243" r:id="rId242" xr:uid="{09D4553A-A858-418C-B252-12DF53E5DDEC}"/>
-    <hyperlink ref="A244" r:id="rId243" xr:uid="{769548BB-09A5-4E6C-A557-6E744AFDF783}"/>
-    <hyperlink ref="A245" r:id="rId244" xr:uid="{C95C9911-49E1-41F3-AA85-4525F4CB5F1E}"/>
-    <hyperlink ref="A246" r:id="rId245" xr:uid="{4F3125FC-B078-4341-9581-DD247FD6F531}"/>
-    <hyperlink ref="A247" r:id="rId246" xr:uid="{F6A3C347-8BCC-455C-93CE-BF65B3667E9A}"/>
-    <hyperlink ref="A248" r:id="rId247" xr:uid="{FD1D48FE-7096-4EDE-81FC-BAC14C3860E1}"/>
-    <hyperlink ref="A249" r:id="rId248" xr:uid="{8AFBB425-F484-4251-BE0C-C791711C3B38}"/>
-    <hyperlink ref="A250" r:id="rId249" xr:uid="{9C79E9C5-7F1B-4FD8-B8EF-7161C9479212}"/>
-    <hyperlink ref="A251" r:id="rId250" xr:uid="{BB34B434-1807-40B1-BB3C-1B48EEB10283}"/>
-    <hyperlink ref="A252" r:id="rId251" xr:uid="{1B912DAA-E7C4-4C44-B6F7-616BAED19392}"/>
-    <hyperlink ref="A253" r:id="rId252" xr:uid="{CD4FE8E4-6DCE-46A8-A915-AA8D96DF32E2}"/>
-    <hyperlink ref="A254" r:id="rId253" xr:uid="{5AEC9357-4CE9-4E8C-828C-E43D86B1A3CC}"/>
-    <hyperlink ref="A255" r:id="rId254" xr:uid="{FB068F2A-6C47-4CFC-9D40-E65B5B5F0ADD}"/>
-    <hyperlink ref="A256" r:id="rId255" xr:uid="{E8A515F9-F583-4D32-9DD6-F6F31659FDC7}"/>
-    <hyperlink ref="A257" r:id="rId256" xr:uid="{A825FD73-47A6-40A5-B370-48BA07996EB8}"/>
-    <hyperlink ref="A258" r:id="rId257" xr:uid="{2A612ED6-8198-40EF-9C82-6D9AFF44FB1D}"/>
-    <hyperlink ref="A259" r:id="rId258" xr:uid="{F7566BB1-3FF7-4795-BEF7-E066EDD9516F}"/>
-    <hyperlink ref="A260" r:id="rId259" xr:uid="{A963FAB1-B4C9-4B32-8DF9-010707D31C03}"/>
-    <hyperlink ref="A261" r:id="rId260" xr:uid="{0B5DA37E-D9A8-4569-B8ED-5FBE65754FD5}"/>
-    <hyperlink ref="A262" r:id="rId261" xr:uid="{83039122-A3FF-45C8-A5AF-AC1975DE99FE}"/>
-    <hyperlink ref="A263" r:id="rId262" xr:uid="{18C1410E-CE88-463B-892B-766E530D2D0A}"/>
-    <hyperlink ref="A264" r:id="rId263" xr:uid="{7CF0CF46-C54A-46E8-8018-E0CEC5F58E34}"/>
-    <hyperlink ref="A265" r:id="rId264" xr:uid="{8660F4B2-577C-4079-944C-BEA649DC77F6}"/>
-    <hyperlink ref="A266" r:id="rId265" xr:uid="{67915459-2DD9-43A6-ABFE-A1F81D1F5BF6}"/>
-    <hyperlink ref="A267" r:id="rId266" xr:uid="{EB573CE6-0337-4CCF-8EDF-0DBB5A1E0693}"/>
-    <hyperlink ref="A268" r:id="rId267" xr:uid="{2DF2E2DB-AA87-482A-847D-77E51D7D4C11}"/>
-    <hyperlink ref="A269" r:id="rId268" xr:uid="{C1DD63F7-FBB4-4A20-8C8D-D3A8FDC73EC2}"/>
-    <hyperlink ref="A270" r:id="rId269" xr:uid="{BAF5A08D-F917-4715-ADC6-6F69E4980BBF}"/>
-    <hyperlink ref="A271" r:id="rId270" xr:uid="{C40F2A17-85F5-472F-BC6C-A9A45A2AB88A}"/>
-    <hyperlink ref="A272" r:id="rId271" xr:uid="{7E030CC5-9532-44FE-86CB-14F56373DF01}"/>
-    <hyperlink ref="A273" r:id="rId272" xr:uid="{8BB1E5E4-817C-434A-B198-B04B7D0B6016}"/>
-    <hyperlink ref="A274" r:id="rId273" xr:uid="{FCA4ABB6-CBBB-4D80-B495-298725A500EB}"/>
-    <hyperlink ref="A275" r:id="rId274" xr:uid="{074F75A0-A263-4094-8EBF-452836B77A17}"/>
-    <hyperlink ref="A276" r:id="rId275" xr:uid="{7A6BF430-320B-4EC3-90F6-3A70360FC836}"/>
-    <hyperlink ref="A277" r:id="rId276" xr:uid="{0B51FDBA-641A-4E0A-B651-73E59064CF50}"/>
-    <hyperlink ref="A278" r:id="rId277" xr:uid="{A7D4A392-7FE9-4C65-8FA7-DB1FE3F19DDD}"/>
-    <hyperlink ref="A279" r:id="rId278" xr:uid="{27AFB0EA-4D33-4C54-A611-0FE437A23EA4}"/>
-    <hyperlink ref="A280" r:id="rId279" xr:uid="{788C5201-2675-4D65-A1E5-949096490F5A}"/>
-    <hyperlink ref="A281" r:id="rId280" xr:uid="{C9E78C4F-3499-49F4-A8C6-FFBE55949576}"/>
-    <hyperlink ref="A282" r:id="rId281" xr:uid="{48302D64-BCEC-4B44-BA04-4F494154CD59}"/>
-    <hyperlink ref="A283" r:id="rId282" xr:uid="{C7220373-1B3B-4110-8156-5E004EB1871E}"/>
-    <hyperlink ref="A284" r:id="rId283" xr:uid="{B7AE266C-A295-4E9A-A151-6DF04AE8DDA8}"/>
-    <hyperlink ref="A285" r:id="rId284" xr:uid="{F485915C-9EC4-4D80-951B-EF48810D2CA5}"/>
-    <hyperlink ref="A286" r:id="rId285" xr:uid="{8718B117-EF89-469B-8C5C-CB0AB8042EB7}"/>
-    <hyperlink ref="A287" r:id="rId286" xr:uid="{5503755D-8D16-40A9-96DB-C3CA02A22462}"/>
-    <hyperlink ref="A288" r:id="rId287" xr:uid="{1F5E27AF-94E4-41F3-8E16-0CCA05E9C1FE}"/>
-    <hyperlink ref="A289" r:id="rId288" xr:uid="{21692353-FC1D-4484-B76D-185254B96373}"/>
-    <hyperlink ref="A290" r:id="rId289" xr:uid="{3517271C-6E0A-4B19-A6FF-C74E6DEAF696}"/>
-    <hyperlink ref="A291" r:id="rId290" xr:uid="{71FEB88D-885D-496A-B9C0-A41B64085DD3}"/>
-    <hyperlink ref="A292" r:id="rId291" xr:uid="{B199811F-C0B5-47F1-842F-46517018BD05}"/>
-    <hyperlink ref="A293" r:id="rId292" xr:uid="{66084828-0F46-493A-8EF6-77AA6037622E}"/>
-    <hyperlink ref="A294" r:id="rId293" xr:uid="{24552C8A-B5B2-484B-B67A-760AFF0A1107}"/>
-    <hyperlink ref="A295" r:id="rId294" xr:uid="{47025D95-24A2-49F3-8EB8-A97167592428}"/>
-    <hyperlink ref="A296" r:id="rId295" xr:uid="{57BB92FD-2CE2-453B-A5DC-5206DB3C41C9}"/>
-    <hyperlink ref="A297" r:id="rId296" xr:uid="{4A5CB7B5-A20A-4430-91BB-396F8AF66FA2}"/>
-    <hyperlink ref="A298" r:id="rId297" xr:uid="{4699AFF0-A697-40DB-9D89-C5531948B0A8}"/>
-    <hyperlink ref="A299" r:id="rId298" xr:uid="{4CB8CD18-A082-4B81-B11B-5FEE1B68D76E}"/>
-    <hyperlink ref="A300" r:id="rId299" xr:uid="{106E32D7-DBC2-4EB2-8976-D389CADDE33C}"/>
-    <hyperlink ref="A301" r:id="rId300" xr:uid="{273EA8B6-AD37-4F91-AEB4-0C4C1212A8E2}"/>
-    <hyperlink ref="A302" r:id="rId301" xr:uid="{2F105CC7-2C3D-45A3-A737-393E3FCDB3E4}"/>
-    <hyperlink ref="A303" r:id="rId302" xr:uid="{5BAEA13F-2BA0-4FD4-B347-D20A4DDDD1CF}"/>
-    <hyperlink ref="A304" r:id="rId303" xr:uid="{DC1D3B3F-AA0B-4251-8541-9DF0B4F1F81E}"/>
-    <hyperlink ref="A305" r:id="rId304" xr:uid="{E18DE4E9-D59B-47EA-81E5-8C1170A7065A}"/>
-    <hyperlink ref="A306" r:id="rId305" xr:uid="{D3C2E758-DFAD-4539-AFF5-32106809ED6D}"/>
-    <hyperlink ref="A307" r:id="rId306" xr:uid="{988BCCE3-E2D4-41A6-9AAF-182EC0314FF0}"/>
-    <hyperlink ref="A308" r:id="rId307" xr:uid="{687C3D28-1F9B-48C9-9551-84DBB6D6E881}"/>
-    <hyperlink ref="A309" r:id="rId308" xr:uid="{9BC9AED9-2D7D-4126-B165-8BD65934579F}"/>
-    <hyperlink ref="A310" r:id="rId309" xr:uid="{934F236F-6939-4EC0-BB65-4094AB5BCBB8}"/>
-    <hyperlink ref="A311" r:id="rId310" xr:uid="{3F17B498-BA99-41CC-A0E2-8A88257FDAF3}"/>
-    <hyperlink ref="A312" r:id="rId311" xr:uid="{95AF7604-4378-4856-BCE2-2439125079CA}"/>
-    <hyperlink ref="A313" r:id="rId312" xr:uid="{5289F217-D282-4408-8CFB-B588BB312014}"/>
-    <hyperlink ref="A314" r:id="rId313" xr:uid="{FA07A58D-06A4-4E9D-A341-38EDE211C747}"/>
-    <hyperlink ref="A315" r:id="rId314" xr:uid="{097D099C-5CF4-414C-AA0F-03B315C42392}"/>
-    <hyperlink ref="A316" r:id="rId315" xr:uid="{86A7867F-ADA1-48A9-BBCF-EA437C385CAD}"/>
-    <hyperlink ref="A317" r:id="rId316" xr:uid="{4D5A9FD0-CA85-4C62-BF65-A250714CBB59}"/>
-    <hyperlink ref="A318" r:id="rId317" xr:uid="{699DB566-B4D2-4A15-BB42-1895E9F3B5E4}"/>
-    <hyperlink ref="A319" r:id="rId318" xr:uid="{D22D874B-8329-4D93-ADEF-8108A94EFC30}"/>
-    <hyperlink ref="A320" r:id="rId319" xr:uid="{913A5489-DBF4-434A-94DA-1E0660FC7009}"/>
-    <hyperlink ref="A321" r:id="rId320" xr:uid="{AA4A8DF5-7395-4972-93A5-A87CA02C30A4}"/>
-    <hyperlink ref="A322" r:id="rId321" xr:uid="{5CACA59A-6D35-4145-BA7D-8A39D3D871F9}"/>
-    <hyperlink ref="A323" r:id="rId322" xr:uid="{223A4119-C924-439B-B42D-F603C27F391B}"/>
-    <hyperlink ref="A324" r:id="rId323" xr:uid="{4CBD3471-10B4-4E3C-B4D0-89A8F5ABD0E6}"/>
-    <hyperlink ref="A325" r:id="rId324" xr:uid="{1A7B1756-0503-4AB4-B4FC-7EB2B98C1417}"/>
-    <hyperlink ref="A326" r:id="rId325" xr:uid="{5B04CC86-E1A9-4B96-B0A9-C87E0388D5D5}"/>
-    <hyperlink ref="A327" r:id="rId326" xr:uid="{623DCA13-890C-4AA9-B6FE-1173F069101B}"/>
-    <hyperlink ref="A328" r:id="rId327" xr:uid="{D8D2B812-02F6-45F7-BE44-5C731F22ED26}"/>
-    <hyperlink ref="A329" r:id="rId328" xr:uid="{E96FFFE6-513A-4E15-9189-7A17173B0E31}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{65C53838-9140-4EEF-9E7A-021D6A69CE42}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{2EF1550C-4C4C-4A56-8845-22013B26FEAA}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{1F0EA047-1731-43A0-AF34-FE5EFD52B25A}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{6F312954-B29B-45FA-89F5-6F18EF1B77D1}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{ECEF2B3E-7E0B-44AB-BD4B-0F59E1CB3584}"/>
+    <hyperlink ref="A7" r:id="rId6" xr:uid="{73E56346-B5B9-41CE-BD40-C4251230AB35}"/>
+    <hyperlink ref="A8" r:id="rId7" xr:uid="{627C2BB3-F987-458C-907F-2E2F00D6B502}"/>
+    <hyperlink ref="A9" r:id="rId8" xr:uid="{E0CA43B7-6B7F-4326-8A75-EFE0E539683F}"/>
+    <hyperlink ref="A10" r:id="rId9" xr:uid="{19B23A34-CB93-4D7D-A521-24517FD07CC0}"/>
+    <hyperlink ref="A11" r:id="rId10" xr:uid="{FA5C2F40-3DC4-4756-8C73-001E75100F73}"/>
+    <hyperlink ref="A12" r:id="rId11" xr:uid="{53A1D025-66B7-4A4F-B2C1-5A108E623227}"/>
+    <hyperlink ref="A13" r:id="rId12" xr:uid="{BA99EFB5-7F06-49E8-A699-526D115765EC}"/>
+    <hyperlink ref="A14" r:id="rId13" xr:uid="{3F8ED4FB-9AE3-4493-9B79-3E83B9E47851}"/>
+    <hyperlink ref="A15" r:id="rId14" xr:uid="{DB73819A-7859-4B4E-9A06-EAEE4D5C32CE}"/>
+    <hyperlink ref="A16" r:id="rId15" xr:uid="{F832D536-7876-44E7-A488-A80314ADC37C}"/>
+    <hyperlink ref="A17" r:id="rId16" xr:uid="{141800C0-130A-4092-AA68-1EA46F53CD71}"/>
+    <hyperlink ref="A18" r:id="rId17" xr:uid="{431D3E15-020E-43AC-A31E-30DFC7A66793}"/>
+    <hyperlink ref="A19" r:id="rId18" xr:uid="{9577E653-AAF2-47A8-8C89-FDC01031233D}"/>
+    <hyperlink ref="A20" r:id="rId19" xr:uid="{D7F46AAC-3585-4E11-B9A0-7DF1F8CCFADC}"/>
+    <hyperlink ref="A21" r:id="rId20" xr:uid="{A2E5FC03-AD84-4618-9E88-59F42E632AF6}"/>
+    <hyperlink ref="A22" r:id="rId21" xr:uid="{486A2050-D087-4F79-8677-EC6CFABD87AA}"/>
+    <hyperlink ref="A23" r:id="rId22" xr:uid="{27ED5C98-8637-4D10-9653-2E589BEED1AF}"/>
+    <hyperlink ref="A24" r:id="rId23" xr:uid="{3A08714F-5320-4D69-A4C9-F11002095544}"/>
+    <hyperlink ref="A25" r:id="rId24" xr:uid="{CAB7BB12-6614-4B69-A464-9B631A38CDE2}"/>
+    <hyperlink ref="A26" r:id="rId25" xr:uid="{5E4FAD2A-24BE-4984-AABA-39231E12C1BC}"/>
+    <hyperlink ref="A27" r:id="rId26" xr:uid="{370401F0-78B0-4718-97F6-3D6A7DDD5AF6}"/>
+    <hyperlink ref="A28" r:id="rId27" xr:uid="{EFB9E40D-83C3-4C65-AFF9-76E397CBEEB7}"/>
+    <hyperlink ref="A29" r:id="rId28" xr:uid="{560122D0-0B70-4344-ACE5-C3930B37C34E}"/>
+    <hyperlink ref="A30" r:id="rId29" xr:uid="{83457946-0454-4152-BF6D-EA5533E7BAF5}"/>
+    <hyperlink ref="A31" r:id="rId30" xr:uid="{938A0942-CAA9-49F0-8C19-84D12316B29D}"/>
+    <hyperlink ref="A32" r:id="rId31" xr:uid="{5E4797C1-589B-4DA7-8A98-584947140299}"/>
+    <hyperlink ref="A33" r:id="rId32" xr:uid="{037355D3-2601-4051-8FC0-E410454515F5}"/>
+    <hyperlink ref="A34" r:id="rId33" xr:uid="{A085487E-47F4-4F8D-8474-E52EF832BC3E}"/>
+    <hyperlink ref="A35" r:id="rId34" xr:uid="{7776B224-4FE5-4CA4-9552-D6E41C6477B4}"/>
+    <hyperlink ref="A36" r:id="rId35" xr:uid="{DE597EDC-8AF4-4026-A484-3160CAC36061}"/>
+    <hyperlink ref="A37" r:id="rId36" xr:uid="{4AACD474-4A5C-4EEE-A1FF-1ADB2DBC2DDA}"/>
+    <hyperlink ref="A38" r:id="rId37" xr:uid="{C68AD6CC-A177-42A8-ABC4-4AE840C2D121}"/>
+    <hyperlink ref="A39" r:id="rId38" xr:uid="{86B293D0-EB60-4BC7-8FF7-7F2C58010BA3}"/>
+    <hyperlink ref="A40" r:id="rId39" xr:uid="{E2F05D84-A641-488B-BFE5-414848AF8300}"/>
+    <hyperlink ref="A41" r:id="rId40" xr:uid="{1F1D1066-D7F9-4D1B-91F9-EA42BAD72B60}"/>
+    <hyperlink ref="A42" r:id="rId41" xr:uid="{6CAE8A67-37BE-4B98-A9B7-E7DBB9A4DD3B}"/>
+    <hyperlink ref="A43" r:id="rId42" xr:uid="{7EA5CF79-2ACA-4090-A416-5D3244B77076}"/>
+    <hyperlink ref="A44" r:id="rId43" xr:uid="{1786923D-BBA5-4B48-8593-5A4916911800}"/>
+    <hyperlink ref="A45" r:id="rId44" xr:uid="{AAFDDA91-4285-4B74-8E80-863268CDEEBD}"/>
+    <hyperlink ref="A46" r:id="rId45" xr:uid="{50ADDAB8-787A-4A43-9347-248729A28835}"/>
+    <hyperlink ref="A47" r:id="rId46" xr:uid="{92B07731-3EDB-4E6A-9149-54973769A6A1}"/>
+    <hyperlink ref="A48" r:id="rId47" xr:uid="{F4DA7E40-E765-4009-B564-025F1040C8F8}"/>
+    <hyperlink ref="A49" r:id="rId48" xr:uid="{992E6CD8-15B2-4015-881A-23CB5AAA40FF}"/>
+    <hyperlink ref="A50" r:id="rId49" xr:uid="{4BC1AB23-B321-4136-A566-8C4FB097F0C7}"/>
+    <hyperlink ref="A51" r:id="rId50" xr:uid="{1D6B9242-55DA-4900-8DF4-D89929B9DFAF}"/>
+    <hyperlink ref="A52" r:id="rId51" xr:uid="{E1BCDD26-BF57-4037-A357-7ECA82CEF67F}"/>
+    <hyperlink ref="A53" r:id="rId52" xr:uid="{9BFBA020-9B09-495F-BB2D-CCF1EBCD2DFA}"/>
+    <hyperlink ref="A54" r:id="rId53" xr:uid="{C742EA80-C012-4BE0-8D2F-5724C16329F3}"/>
+    <hyperlink ref="A55" r:id="rId54" xr:uid="{DAF25C5B-CDF3-4D50-AE30-8F6110A5746E}"/>
+    <hyperlink ref="A56" r:id="rId55" xr:uid="{7B4D254E-B482-4787-A486-02F4A495708B}"/>
+    <hyperlink ref="A57" r:id="rId56" xr:uid="{0B7D2101-B475-4C25-8751-3B43472DC036}"/>
+    <hyperlink ref="A58" r:id="rId57" xr:uid="{4D6E20B0-E19E-4851-907D-991C279F20B6}"/>
+    <hyperlink ref="A59" r:id="rId58" xr:uid="{E0942D8C-E2B1-49A1-A75A-D496E8368510}"/>
+    <hyperlink ref="A60" r:id="rId59" xr:uid="{8BD1AD86-ED31-4AB6-A7BE-A688EA4A1B69}"/>
+    <hyperlink ref="A61" r:id="rId60" xr:uid="{3A73E481-C0C7-4FC3-B714-BCFA52050CB1}"/>
+    <hyperlink ref="A62" r:id="rId61" xr:uid="{E84AEF88-E034-47E8-BCA3-32EE66FBF5D3}"/>
+    <hyperlink ref="A63" r:id="rId62" xr:uid="{18C5F30D-4C55-4716-B9A6-209B3F605E09}"/>
+    <hyperlink ref="A64" r:id="rId63" xr:uid="{402E4EA8-623C-4A01-B6D9-5039AE7B2BB2}"/>
+    <hyperlink ref="A65" r:id="rId64" xr:uid="{D9CB4FCB-4445-4E06-A396-6EE93C8AEBB9}"/>
+    <hyperlink ref="A66" r:id="rId65" xr:uid="{A23983BE-85D1-430E-BA0A-67EDFF68605A}"/>
+    <hyperlink ref="A67" r:id="rId66" xr:uid="{71D1075C-8177-4593-B64D-FB0AE602D9AE}"/>
+    <hyperlink ref="A68" r:id="rId67" xr:uid="{2C76BE5B-C7EB-4D69-8A81-5E86E95A2780}"/>
+    <hyperlink ref="A69" r:id="rId68" xr:uid="{9CF17C69-D7FF-4D39-ACA7-6C4EB0E173F5}"/>
+    <hyperlink ref="A70" r:id="rId69" xr:uid="{BF43EEC9-E011-45D4-82A4-779FB6EF2002}"/>
+    <hyperlink ref="A71" r:id="rId70" xr:uid="{088ED598-A756-40A6-866A-5DE84774E5A1}"/>
+    <hyperlink ref="A72" r:id="rId71" xr:uid="{74AB3BE3-CF92-4BBB-952E-F37320AB093D}"/>
+    <hyperlink ref="A73" r:id="rId72" xr:uid="{BE1EE099-46F0-4D8F-B90C-ADE312290EEB}"/>
+    <hyperlink ref="A74" r:id="rId73" xr:uid="{D56D0B10-3F5E-4092-9409-64EF91601E33}"/>
+    <hyperlink ref="A75" r:id="rId74" xr:uid="{64AFD3E8-4692-41D2-ACDC-C66BB86A070B}"/>
+    <hyperlink ref="A76" r:id="rId75" xr:uid="{7F06F0B5-105E-4C2A-A0F9-D9B3020EFEE7}"/>
+    <hyperlink ref="A77" r:id="rId76" xr:uid="{EB6892B3-5E16-4EEE-86D9-7114C03D4A11}"/>
+    <hyperlink ref="A78" r:id="rId77" xr:uid="{23C8C53B-4501-4B5A-80B5-734FB508094D}"/>
+    <hyperlink ref="A79" r:id="rId78" xr:uid="{ECE43080-E828-448C-A86B-9CC03AA45636}"/>
+    <hyperlink ref="A80" r:id="rId79" xr:uid="{48C1A0F2-5111-4B2F-806C-D59AB362363C}"/>
+    <hyperlink ref="A81" r:id="rId80" xr:uid="{26851266-492C-4FBD-ABF2-C7BA3C129BF7}"/>
+    <hyperlink ref="A82" r:id="rId81" xr:uid="{7B2B56F3-E859-434D-8A33-8FF139776739}"/>
+    <hyperlink ref="A83" r:id="rId82" xr:uid="{C7583F65-4CE8-4CDB-A82A-6FC5045EBEEE}"/>
+    <hyperlink ref="A84" r:id="rId83" xr:uid="{92B4112D-388F-498E-A9E5-8CD912A139E1}"/>
+    <hyperlink ref="A85" r:id="rId84" xr:uid="{9A8F2C29-4339-4014-A473-E38E1DBCBEAB}"/>
+    <hyperlink ref="A86" r:id="rId85" xr:uid="{8DE06025-EEDB-4201-BD3B-A5B62CAEED7A}"/>
+    <hyperlink ref="A87" r:id="rId86" xr:uid="{00C3BF7C-271D-4D57-8D3E-D78B728F84A2}"/>
+    <hyperlink ref="A88" r:id="rId87" xr:uid="{EDE71EBB-53F5-43C6-B6A7-5A614A8869F7}"/>
+    <hyperlink ref="A89" r:id="rId88" xr:uid="{E2895AD8-88F2-40F0-BE12-11F7AB9FBF4F}"/>
+    <hyperlink ref="A90" r:id="rId89" xr:uid="{EC8536C5-DCBE-4645-9CEA-D9B2767795A6}"/>
+    <hyperlink ref="A91" r:id="rId90" xr:uid="{F8446171-38E1-4934-A854-310FB292CED8}"/>
+    <hyperlink ref="A92" r:id="rId91" xr:uid="{B2E60E8D-5043-42BE-9048-5EBB38F3C42B}"/>
+    <hyperlink ref="A93" r:id="rId92" xr:uid="{C9D94EBE-202B-4110-9F82-BE27CEFA61BB}"/>
+    <hyperlink ref="A94" r:id="rId93" xr:uid="{CB068740-250A-4E51-B121-7F6952EE59FB}"/>
+    <hyperlink ref="A95" r:id="rId94" xr:uid="{F4E46799-15E9-40E5-A5FA-92A069022C76}"/>
+    <hyperlink ref="A96" r:id="rId95" xr:uid="{0FE493E0-2F2F-4BCB-B641-57D7B041B6DB}"/>
+    <hyperlink ref="A97" r:id="rId96" xr:uid="{A2D6F7D3-CF84-4098-942B-5AC228821AD3}"/>
+    <hyperlink ref="A98" r:id="rId97" xr:uid="{20B9D061-28BF-4211-8080-B409F27719C7}"/>
+    <hyperlink ref="A99" r:id="rId98" xr:uid="{E50ACF42-E608-49C0-ACB0-13A3E536618B}"/>
+    <hyperlink ref="A100" r:id="rId99" xr:uid="{7B56F8A3-FA9F-4C6B-BD96-AC4B41FDE1E4}"/>
+    <hyperlink ref="A101" r:id="rId100" xr:uid="{EF6004E8-670C-4FDF-9DA0-077C52C0C615}"/>
+    <hyperlink ref="A102" r:id="rId101" xr:uid="{8A8E371F-5B8E-4050-A851-D7CD11B66C5D}"/>
+    <hyperlink ref="A103" r:id="rId102" xr:uid="{AC87322E-AA1C-416D-B81E-6D8CABE558F8}"/>
+    <hyperlink ref="A104" r:id="rId103" xr:uid="{96E035E9-CFA3-471B-84E7-ABE06E6B1A00}"/>
+    <hyperlink ref="A105" r:id="rId104" xr:uid="{E7CEB3FF-587F-4A7F-8C8B-A4FD30852D87}"/>
+    <hyperlink ref="A106" r:id="rId105" xr:uid="{1520EC3B-5142-4014-8A97-92902A6B4430}"/>
+    <hyperlink ref="A107" r:id="rId106" xr:uid="{9BD8E78C-08B2-4086-9FBA-2C6EBB487557}"/>
+    <hyperlink ref="A108" r:id="rId107" xr:uid="{0B376492-D083-449A-98C1-DBEC2015BD45}"/>
+    <hyperlink ref="A109" r:id="rId108" xr:uid="{12AB0B89-C53C-4023-BDCE-443EC6B805BF}"/>
+    <hyperlink ref="A110" r:id="rId109" xr:uid="{EB8D5CE1-3346-48CA-A7EC-5D91B323DE7E}"/>
+    <hyperlink ref="A111" r:id="rId110" xr:uid="{184157C9-0A27-47C4-AED1-D3A316A6188C}"/>
+    <hyperlink ref="A112" r:id="rId111" xr:uid="{2745613A-AC04-4663-ADD7-83FBE846505B}"/>
+    <hyperlink ref="A113" r:id="rId112" xr:uid="{53330622-F142-4D55-883D-C4B9999DB177}"/>
+    <hyperlink ref="A114" r:id="rId113" xr:uid="{BFBB6C70-13F9-432E-BCD0-AFDAEBB2847F}"/>
+    <hyperlink ref="A115" r:id="rId114" xr:uid="{0D74F811-203D-4CDF-A774-08053E00BD1B}"/>
+    <hyperlink ref="A116" r:id="rId115" xr:uid="{8C6ED213-4E4D-49C2-BA6F-127098E34F5D}"/>
+    <hyperlink ref="A117" r:id="rId116" xr:uid="{71136123-B523-4474-9AAE-FF8E2034699C}"/>
+    <hyperlink ref="A118" r:id="rId117" xr:uid="{BCDE2261-3595-4917-988D-CD76A5547312}"/>
+    <hyperlink ref="A119" r:id="rId118" xr:uid="{AF0C6F5E-A0A0-4304-A4D6-F20A9FA53E68}"/>
+    <hyperlink ref="A120" r:id="rId119" xr:uid="{AE07B91E-9BB3-4BB8-A0A8-3EE4394D83B4}"/>
+    <hyperlink ref="A121" r:id="rId120" xr:uid="{6BBCCA7F-2518-4C0B-973B-E3235A2F9A1B}"/>
+    <hyperlink ref="A122" r:id="rId121" xr:uid="{33F0DCA8-EC4C-42F7-9B6D-53C19D9E4F36}"/>
+    <hyperlink ref="A123" r:id="rId122" xr:uid="{9A427E8D-1F7F-4BFE-A310-236FB4EC4F12}"/>
+    <hyperlink ref="A124" r:id="rId123" xr:uid="{87CC261E-8D1F-46BC-BB80-BE734C2A7B45}"/>
+    <hyperlink ref="A125" r:id="rId124" xr:uid="{145030C7-E119-48E8-9084-54904C1A9A14}"/>
+    <hyperlink ref="A126" r:id="rId125" xr:uid="{3E88F464-E1AE-4C90-BDEB-1CDA09B856FB}"/>
+    <hyperlink ref="A127" r:id="rId126" xr:uid="{5FE0231E-7785-45A9-B9E6-E23354EB06D7}"/>
+    <hyperlink ref="A128" r:id="rId127" xr:uid="{AFFF1669-E5BE-4FB6-A386-14CACAC92AAE}"/>
+    <hyperlink ref="A129" r:id="rId128" xr:uid="{A5946B51-13AD-47FA-BA22-555028E263A5}"/>
+    <hyperlink ref="A130" r:id="rId129" xr:uid="{2CC7E497-DE55-4410-91FE-D92DBC0ACE71}"/>
+    <hyperlink ref="A131" r:id="rId130" xr:uid="{CF526875-FC72-4E37-9AF0-BAA690D4BFB3}"/>
+    <hyperlink ref="A132" r:id="rId131" xr:uid="{DB01FDB3-56A4-4A9A-9BCF-F93AA3873BF6}"/>
+    <hyperlink ref="A133" r:id="rId132" xr:uid="{E569EFAF-6ECC-4C37-AA5A-7E536E1F640A}"/>
+    <hyperlink ref="A134" r:id="rId133" xr:uid="{9E0A921F-560E-4C05-8718-B30829FD49B6}"/>
+    <hyperlink ref="A135" r:id="rId134" xr:uid="{0A0A95B2-0B47-4CE1-8829-621511AB2EBB}"/>
+    <hyperlink ref="A136" r:id="rId135" xr:uid="{B286A83C-03AF-4B4D-A7E7-BF9476F07396}"/>
+    <hyperlink ref="A137" r:id="rId136" xr:uid="{D49A2101-0249-447A-BD78-715A586D36AD}"/>
+    <hyperlink ref="A138" r:id="rId137" xr:uid="{BA83F56D-2B30-4728-BC2B-DCCC0491B2D0}"/>
+    <hyperlink ref="A139" r:id="rId138" xr:uid="{73B052FB-8618-43E8-98F9-C08C2460E1F6}"/>
+    <hyperlink ref="A140" r:id="rId139" xr:uid="{263AFE1C-D326-4F07-975F-CC579CDC351A}"/>
+    <hyperlink ref="A141" r:id="rId140" xr:uid="{B823D89E-52A1-498C-B548-AD6AE4468D08}"/>
+    <hyperlink ref="A142" r:id="rId141" xr:uid="{E9D90AAF-B630-4A1B-A8A2-5A54B2EC8B97}"/>
+    <hyperlink ref="A143" r:id="rId142" xr:uid="{31C2D060-F608-4C74-BD90-09332024599E}"/>
+    <hyperlink ref="A144" r:id="rId143" xr:uid="{8DD6590D-6650-47A7-BD35-9DE958534D66}"/>
+    <hyperlink ref="A145" r:id="rId144" xr:uid="{9DBDB07F-4460-4E6C-A35B-59FC49F08928}"/>
+    <hyperlink ref="A146" r:id="rId145" xr:uid="{E1C4BC8B-A558-48AF-8D54-C1F5C7953E59}"/>
+    <hyperlink ref="A147" r:id="rId146" xr:uid="{14E2C2EC-1A9D-4B9F-98AE-C522BA97FA54}"/>
+    <hyperlink ref="A148" r:id="rId147" xr:uid="{7971A941-1B23-4D4E-B8C1-1F2CD9526F27}"/>
+    <hyperlink ref="A149" r:id="rId148" xr:uid="{E9F5D77D-6A24-4945-A134-929A517EFA05}"/>
+    <hyperlink ref="A150" r:id="rId149" xr:uid="{99B58546-F50A-44EE-9ED8-D7E902F48C6F}"/>
+    <hyperlink ref="A151" r:id="rId150" xr:uid="{93120FCD-E5B4-4819-8A66-E0424F5D81F2}"/>
+    <hyperlink ref="A152" r:id="rId151" xr:uid="{3F89FFEF-C277-43EE-95A7-9CD08AFA552A}"/>
+    <hyperlink ref="A153" r:id="rId152" xr:uid="{2504111A-9EA1-467D-A2F1-4E209CFDCD3F}"/>
+    <hyperlink ref="A154" r:id="rId153" xr:uid="{2034CE9D-DCD3-41E8-9F04-673094DE0BC5}"/>
+    <hyperlink ref="A155" r:id="rId154" xr:uid="{731F2EA2-920F-4462-9469-C9E8D52BCC88}"/>
+    <hyperlink ref="A156" r:id="rId155" xr:uid="{2F2913BB-3A52-4E03-9B96-ECFF93395E51}"/>
+    <hyperlink ref="A157" r:id="rId156" xr:uid="{E8D9A628-31AF-4ACF-BD3E-83B59FF2FD29}"/>
+    <hyperlink ref="A158" r:id="rId157" xr:uid="{330E9EA6-916E-435F-8FA0-39A3CC63AF15}"/>
+    <hyperlink ref="A159" r:id="rId158" xr:uid="{4DC3D9E4-CA9B-4713-80CA-657DE8733ABB}"/>
+    <hyperlink ref="A160" r:id="rId159" xr:uid="{83DC37B1-2EC1-48EF-AA02-98F3C3C9101B}"/>
+    <hyperlink ref="A161" r:id="rId160" xr:uid="{BE945072-E3D7-4FD3-9802-6A18758503E4}"/>
+    <hyperlink ref="A162" r:id="rId161" xr:uid="{C77164B3-4800-4029-89BD-FA620349C802}"/>
+    <hyperlink ref="A163" r:id="rId162" xr:uid="{F49DFF58-7379-4020-9741-26A334A3B208}"/>
+    <hyperlink ref="A164" r:id="rId163" xr:uid="{2F8BA383-DADA-44E2-AC8D-2CD6651EB051}"/>
+    <hyperlink ref="A165" r:id="rId164" xr:uid="{06970B85-C220-4320-BB12-8622CE6F9973}"/>
+    <hyperlink ref="A166" r:id="rId165" xr:uid="{19A15C5C-4149-40CD-8442-66ECDA98BC9A}"/>
+    <hyperlink ref="A167" r:id="rId166" xr:uid="{4560280B-D1F7-43F9-B605-A238B0910355}"/>
+    <hyperlink ref="A168" r:id="rId167" xr:uid="{BCE276CE-7FFF-47F0-B6A3-514E12A476F1}"/>
+    <hyperlink ref="A169" r:id="rId168" xr:uid="{2A25D041-3026-4493-9EF1-C5E0BD86D635}"/>
+    <hyperlink ref="A170" r:id="rId169" xr:uid="{4AD8DF4D-AC19-4389-878A-76866BFEFF34}"/>
+    <hyperlink ref="A171" r:id="rId170" xr:uid="{F12F6902-02A1-4DB3-A593-6A961333F36B}"/>
+    <hyperlink ref="A172" r:id="rId171" xr:uid="{2334EFE3-E3F1-4ED0-BCA8-0E5DE53D45E8}"/>
+    <hyperlink ref="A173" r:id="rId172" xr:uid="{5D83C85F-83BA-4335-8D5B-3C9F6671AB3D}"/>
+    <hyperlink ref="A174" r:id="rId173" xr:uid="{2229141D-CB8D-4A43-86C3-DD69D4D91CAB}"/>
+    <hyperlink ref="A175" r:id="rId174" xr:uid="{F72FD3B6-048B-4731-81E8-2E6D46821411}"/>
+    <hyperlink ref="A176" r:id="rId175" xr:uid="{4B9C4BE3-3C46-43FE-8B8B-F9A531716611}"/>
+    <hyperlink ref="A177" r:id="rId176" xr:uid="{8032E7F1-0E4F-4459-8923-FAAE2E0AE756}"/>
+    <hyperlink ref="A178" r:id="rId177" xr:uid="{09502D2B-F1E0-402A-855A-5F34D0F3E6E2}"/>
+    <hyperlink ref="A179" r:id="rId178" xr:uid="{C2E8DB82-6DF2-445B-8730-2784D881AF98}"/>
+    <hyperlink ref="A180" r:id="rId179" xr:uid="{6F11F233-2740-4CCC-BCB3-51E22D018801}"/>
+    <hyperlink ref="A181" r:id="rId180" xr:uid="{214CA737-2CE7-43AB-B147-DC99D71385EE}"/>
+    <hyperlink ref="A182" r:id="rId181" xr:uid="{F0D5509A-6555-4155-B4A8-FE89DB95108C}"/>
+    <hyperlink ref="A183" r:id="rId182" xr:uid="{27FD9110-86FC-4DDA-87D9-BA1E71EBB4D4}"/>
+    <hyperlink ref="A184" r:id="rId183" xr:uid="{A1FFCCB8-51F4-4AC7-8F4D-4F995B68974F}"/>
+    <hyperlink ref="A185" r:id="rId184" xr:uid="{FD2E0A56-15D5-4F04-A5A0-CCADA005ACDE}"/>
+    <hyperlink ref="A186" r:id="rId185" xr:uid="{FC656027-304F-4485-8DAA-CC5D27BBC9EC}"/>
+    <hyperlink ref="A187" r:id="rId186" xr:uid="{07BF0F99-225F-4C8E-8827-EF433B01CB83}"/>
+    <hyperlink ref="A188" r:id="rId187" xr:uid="{429AF3D6-FF84-44EC-BBD5-955CFAF32C15}"/>
+    <hyperlink ref="A189" r:id="rId188" xr:uid="{3641547A-5FD5-4F7F-969A-8F0281181748}"/>
+    <hyperlink ref="A190" r:id="rId189" xr:uid="{449913B1-8B39-40A4-A937-BE448D07DCAB}"/>
+    <hyperlink ref="A191" r:id="rId190" xr:uid="{D464190E-573A-4083-A60A-564533151C6F}"/>
+    <hyperlink ref="A192" r:id="rId191" xr:uid="{AFCAEF61-F9A5-4644-8310-B4C0209D6A14}"/>
+    <hyperlink ref="A193" r:id="rId192" xr:uid="{822F87FD-8958-44CF-9670-F18F02C9D9CB}"/>
+    <hyperlink ref="A194" r:id="rId193" xr:uid="{BDA0C1CD-68E3-46FE-A69D-6B6902269B4D}"/>
+    <hyperlink ref="A195" r:id="rId194" xr:uid="{A36C7BAA-3B1A-4C65-842C-53CDEB5850B9}"/>
+    <hyperlink ref="A196" r:id="rId195" xr:uid="{57D7B479-1A01-4CFA-9B68-F8C6542177B1}"/>
+    <hyperlink ref="A197" r:id="rId196" xr:uid="{3CABEB56-F974-44D0-BEC0-23ED8A13C83D}"/>
+    <hyperlink ref="A198" r:id="rId197" xr:uid="{B00B10DD-B471-410A-A532-324E770487D5}"/>
+    <hyperlink ref="A199" r:id="rId198" xr:uid="{A0246F3E-8FBD-4506-8D1B-83134E20D77E}"/>
+    <hyperlink ref="A200" r:id="rId199" xr:uid="{CFF4F513-D970-4602-AC02-752AB30580BB}"/>
+    <hyperlink ref="A201" r:id="rId200" xr:uid="{0966A6C8-AA3B-40CA-8CA7-BFC10D78B7EE}"/>
+    <hyperlink ref="A202" r:id="rId201" xr:uid="{89660F12-07E8-4F67-AEBC-780CDF8F631C}"/>
+    <hyperlink ref="A203" r:id="rId202" xr:uid="{D987BB1F-4659-4563-8B2F-5A093BD331F4}"/>
+    <hyperlink ref="A204" r:id="rId203" xr:uid="{2868833C-A217-4F6B-A83D-8612E0848989}"/>
+    <hyperlink ref="A205" r:id="rId204" xr:uid="{F5CD6E94-D9ED-4E21-BFE7-61C426F541B3}"/>
+    <hyperlink ref="A206" r:id="rId205" xr:uid="{954A7EA2-1780-4949-BABE-543DBEC2D462}"/>
+    <hyperlink ref="A207" r:id="rId206" xr:uid="{92FA01DF-DE2E-49D6-9A82-554DEC831CBD}"/>
+    <hyperlink ref="A208" r:id="rId207" xr:uid="{AB48353D-2989-46BA-90E5-14DB0329FC07}"/>
+    <hyperlink ref="A209" r:id="rId208" xr:uid="{B2AE9381-A4AA-4A89-B9FA-1C750AE92F16}"/>
+    <hyperlink ref="A210" r:id="rId209" xr:uid="{44D59BFF-227B-4B6A-9468-ED892613F58E}"/>
+    <hyperlink ref="A211" r:id="rId210" xr:uid="{D152C45C-E2D1-4617-A383-08E82B03486E}"/>
+    <hyperlink ref="A212" r:id="rId211" xr:uid="{3C41905B-C579-4614-8FA6-20C0CD1FE67B}"/>
+    <hyperlink ref="A213" r:id="rId212" xr:uid="{CBA64AC3-AB62-429E-AA0B-15B755F0A9FB}"/>
+    <hyperlink ref="A214" r:id="rId213" xr:uid="{6957A3D7-B46D-4155-8126-EE138DE2A0DE}"/>
+    <hyperlink ref="A215" r:id="rId214" xr:uid="{677FA4BE-0662-4AD6-BF64-E17EDEA9FF16}"/>
+    <hyperlink ref="A216" r:id="rId215" xr:uid="{93463334-D868-46AB-BF4B-2E0B800A6CDD}"/>
+    <hyperlink ref="A217" r:id="rId216" xr:uid="{34A778EE-C4A5-4BB9-9C90-EC1B8216D5CB}"/>
+    <hyperlink ref="A218" r:id="rId217" xr:uid="{448FB53A-3731-4006-BA37-719446736ED0}"/>
+    <hyperlink ref="A219" r:id="rId218" xr:uid="{D90C6A56-57CB-4DE1-B8F0-D8D507AAEA5D}"/>
+    <hyperlink ref="A220" r:id="rId219" xr:uid="{1252B817-C0AC-456C-AFEB-AA137131CAAF}"/>
+    <hyperlink ref="A221" r:id="rId220" xr:uid="{15660DDD-08A7-48B8-8858-930C5FC6D225}"/>
+    <hyperlink ref="A222" r:id="rId221" xr:uid="{3495CFCE-585D-4177-9AF9-65AB73379E40}"/>
+    <hyperlink ref="A223" r:id="rId222" xr:uid="{1EC0288A-919B-4804-89F6-BE73A9AEF0CA}"/>
+    <hyperlink ref="A224" r:id="rId223" xr:uid="{CDA114CF-314D-47E8-8C3F-2E3F6B6D8F6D}"/>
+    <hyperlink ref="A225" r:id="rId224" xr:uid="{B6D860EA-AE55-40AD-A7FE-34A160EE0A0B}"/>
+    <hyperlink ref="A226" r:id="rId225" xr:uid="{9ABA3B6E-A84B-40DA-A46F-FA4511BBBC86}"/>
+    <hyperlink ref="A227" r:id="rId226" xr:uid="{812AC9EE-BB73-416C-8ECD-4A7CB0AB83E7}"/>
+    <hyperlink ref="A228" r:id="rId227" xr:uid="{9F7BE427-7E2D-4BCB-8B27-058A495E1B17}"/>
+    <hyperlink ref="A229" r:id="rId228" xr:uid="{43E6C1C4-F21A-436A-8701-900CA36A1840}"/>
+    <hyperlink ref="A230" r:id="rId229" xr:uid="{768D7589-A0D6-4E0D-B037-978DFDA0CE72}"/>
+    <hyperlink ref="A231" r:id="rId230" xr:uid="{F4DC90EF-F3A5-4929-96B3-6F1F15EE7660}"/>
+    <hyperlink ref="A232" r:id="rId231" xr:uid="{041A82DC-307F-42FB-B8E4-32DB340432E7}"/>
+    <hyperlink ref="A233" r:id="rId232" xr:uid="{ABFDF0C1-9272-4FBC-896F-DD434EB0E823}"/>
+    <hyperlink ref="A234" r:id="rId233" xr:uid="{87C729ED-C2E3-4CD5-B525-9349C18A9BF3}"/>
+    <hyperlink ref="A235" r:id="rId234" xr:uid="{341E860B-6185-4B31-B0D8-E77EEA6667AE}"/>
+    <hyperlink ref="A236" r:id="rId235" xr:uid="{0EC62943-11AD-4869-990E-6C1BA2DB3C0A}"/>
+    <hyperlink ref="A237" r:id="rId236" xr:uid="{98AF1E7E-B2FF-49EF-8BAB-594DC05E5D6B}"/>
+    <hyperlink ref="A238" r:id="rId237" xr:uid="{221D6093-0DFF-4E14-85E2-B2B7133CD8AF}"/>
+    <hyperlink ref="A239" r:id="rId238" xr:uid="{E039C702-A17A-4E0E-818D-E4FF3917DF99}"/>
+    <hyperlink ref="A240" r:id="rId239" xr:uid="{A9194092-3776-4926-B5D6-511739CE5349}"/>
+    <hyperlink ref="A241" r:id="rId240" xr:uid="{A2B0BF1E-C0C9-4313-AB29-2E64577ADEDA}"/>
+    <hyperlink ref="A242" r:id="rId241" xr:uid="{BD8E84F7-F03A-4C8D-9022-806BD0AD0E03}"/>
+    <hyperlink ref="A243" r:id="rId242" xr:uid="{3E8C15F7-3B86-423C-B8A4-812A0101708C}"/>
+    <hyperlink ref="A244" r:id="rId243" xr:uid="{A86CC891-F6E3-437F-BA0D-203F2171B280}"/>
+    <hyperlink ref="A245" r:id="rId244" xr:uid="{A0E2A253-B3A1-4B2E-A074-85F8B13EB7D8}"/>
+    <hyperlink ref="A246" r:id="rId245" xr:uid="{EA4DAA3A-B19B-4912-A8E2-6127214D9E7A}"/>
+    <hyperlink ref="A247" r:id="rId246" xr:uid="{78138C71-517C-4651-B7B9-D171DE70CB3E}"/>
+    <hyperlink ref="A248" r:id="rId247" xr:uid="{7AB81EC5-2E22-4929-A75A-E9E9380FDCEC}"/>
+    <hyperlink ref="A249" r:id="rId248" xr:uid="{7082DC6E-1E97-426F-B5A3-A45AEB5914FF}"/>
+    <hyperlink ref="A250" r:id="rId249" xr:uid="{CECDA91C-B682-443D-8D7C-276046F48F55}"/>
+    <hyperlink ref="A251" r:id="rId250" xr:uid="{AB6917E0-8891-4FFA-BC2C-5F4D6787E48D}"/>
+    <hyperlink ref="A252" r:id="rId251" xr:uid="{A5F5360D-E327-4762-B6AC-6A671CA86874}"/>
+    <hyperlink ref="A253" r:id="rId252" xr:uid="{641A338E-6F9B-402A-B42B-1F8F77DE6515}"/>
+    <hyperlink ref="A254" r:id="rId253" xr:uid="{A3DF0028-5319-4F98-A33A-6CA9E76B24E8}"/>
+    <hyperlink ref="A255" r:id="rId254" xr:uid="{880AC2D0-5DBA-44C0-B303-3AD21496ACB6}"/>
+    <hyperlink ref="A256" r:id="rId255" xr:uid="{551EEB20-7BA0-4F17-9EC7-93D9291E2C00}"/>
+    <hyperlink ref="A257" r:id="rId256" xr:uid="{547B7AD1-5F31-4398-8793-6A104153F932}"/>
+    <hyperlink ref="A258" r:id="rId257" xr:uid="{67BADEC7-4AA3-4D07-8BE0-A378CACF58EE}"/>
+    <hyperlink ref="A259" r:id="rId258" xr:uid="{F350697F-11E3-4792-B97D-11E93F36D4D9}"/>
+    <hyperlink ref="A260" r:id="rId259" xr:uid="{F5E34C1E-0272-4B97-8BC2-592814A2AF5D}"/>
+    <hyperlink ref="A261" r:id="rId260" xr:uid="{495F6F66-AB75-43E4-A913-05CA2342E0A7}"/>
+    <hyperlink ref="A262" r:id="rId261" xr:uid="{FDEF19AB-34ED-49BE-B899-FC5DBBB08AE3}"/>
+    <hyperlink ref="A263" r:id="rId262" xr:uid="{87B93B9D-288E-4BCA-AC86-C9869DEFDFA3}"/>
+    <hyperlink ref="A264" r:id="rId263" xr:uid="{23A5F29C-EB8B-4780-97B9-951FD6841195}"/>
+    <hyperlink ref="A265" r:id="rId264" xr:uid="{FC1A1944-AB0C-4FFF-A1F5-8327A0BD507F}"/>
+    <hyperlink ref="A266" r:id="rId265" xr:uid="{FD4A5D04-D547-4938-893A-7E2F66A6BE62}"/>
+    <hyperlink ref="A267" r:id="rId266" xr:uid="{BF3A5B2C-D97E-4ECD-8D9F-6FC11984E7D2}"/>
+    <hyperlink ref="A268" r:id="rId267" xr:uid="{5A87BF4C-3C56-48F7-A60E-ECE95873AD3F}"/>
+    <hyperlink ref="A269" r:id="rId268" xr:uid="{DA38326E-4075-4DD1-800F-0E6D22D22B27}"/>
+    <hyperlink ref="A270" r:id="rId269" xr:uid="{5C992E6C-AC1E-4C53-8D08-690F39CE023B}"/>
+    <hyperlink ref="A271" r:id="rId270" xr:uid="{EBAAC7AC-77C5-4DC8-A2A6-6814D167DE76}"/>
+    <hyperlink ref="A272" r:id="rId271" xr:uid="{9E0CF58A-08AD-4E0F-90B3-A8AC4FD65FCD}"/>
+    <hyperlink ref="A273" r:id="rId272" xr:uid="{2F564192-6EEB-4FBE-838B-4A5696ED67A7}"/>
+    <hyperlink ref="A274" r:id="rId273" xr:uid="{868AF271-617C-4EDC-9290-61EFC1B5027C}"/>
+    <hyperlink ref="A275" r:id="rId274" xr:uid="{0DE9CED1-D21E-472D-BCF5-F42A8510B0FC}"/>
+    <hyperlink ref="A276" r:id="rId275" xr:uid="{D3B095C5-B71C-4107-8F24-B5B892ECCADE}"/>
+    <hyperlink ref="A277" r:id="rId276" xr:uid="{570F7B57-4FA3-4782-B7A3-0FE963EF3B2C}"/>
+    <hyperlink ref="A278" r:id="rId277" xr:uid="{7A3774AF-292A-40C2-95A9-B21E7EEC3849}"/>
+    <hyperlink ref="A279" r:id="rId278" xr:uid="{1645BA8B-1E14-4C7A-A3D1-103E39F64EA7}"/>
+    <hyperlink ref="A280" r:id="rId279" xr:uid="{7D61017E-30A9-4AA2-9FB6-E3A21958C409}"/>
+    <hyperlink ref="A281" r:id="rId280" xr:uid="{01938150-62EC-4ABA-B881-48696D7EDA96}"/>
+    <hyperlink ref="A282" r:id="rId281" xr:uid="{47129927-24EC-4827-A646-082EBF5E3E4B}"/>
+    <hyperlink ref="A283" r:id="rId282" xr:uid="{8E3BBE84-2245-494A-8A81-EED21C6579B1}"/>
+    <hyperlink ref="A284" r:id="rId283" xr:uid="{CC282807-DFE1-4C6D-B765-299EF74C53D0}"/>
+    <hyperlink ref="A285" r:id="rId284" xr:uid="{22607D85-AF49-43E1-A9FF-B78BEA81D26E}"/>
+    <hyperlink ref="A286" r:id="rId285" xr:uid="{125B88CB-8A3D-4F0E-BA92-8AF79E93015B}"/>
+    <hyperlink ref="A287" r:id="rId286" xr:uid="{EB4C5E5E-7574-4BD5-9769-69FB6623435B}"/>
+    <hyperlink ref="A288" r:id="rId287" xr:uid="{D4DB8019-0FE4-4D45-B237-68D9CF7611AE}"/>
+    <hyperlink ref="A289" r:id="rId288" xr:uid="{499AE2E8-6285-4B38-83BE-78E49FD8C329}"/>
+    <hyperlink ref="A290" r:id="rId289" xr:uid="{9D54051F-B246-4C39-AAD1-56D5B1AC660C}"/>
+    <hyperlink ref="A291" r:id="rId290" xr:uid="{F6D644BC-2EC1-4402-A15F-552818218FD4}"/>
+    <hyperlink ref="A292" r:id="rId291" xr:uid="{C2FAF3C0-7460-44AB-BE18-D01F2DB4B8F6}"/>
+    <hyperlink ref="A293" r:id="rId292" xr:uid="{FA1377DC-0227-4BF9-9105-75E4641D018A}"/>
+    <hyperlink ref="A294" r:id="rId293" xr:uid="{25B4DFF0-702A-4643-A94F-891D7404A315}"/>
+    <hyperlink ref="A295" r:id="rId294" xr:uid="{783FE978-6CD3-4DBA-9789-1D28CA8C62A3}"/>
+    <hyperlink ref="A296" r:id="rId295" xr:uid="{C48DBEBB-CCAC-4582-B5A3-DA92BD35B36D}"/>
+    <hyperlink ref="A297" r:id="rId296" xr:uid="{8A7B42FF-2E8C-4185-8C54-737E73D9FF27}"/>
+    <hyperlink ref="A298" r:id="rId297" xr:uid="{8FAF4C51-8F98-4897-B9B5-70E96DCD853A}"/>
+    <hyperlink ref="A299" r:id="rId298" xr:uid="{5D904DBE-254A-4AFF-91B5-702D6D7D20F7}"/>
+    <hyperlink ref="A300" r:id="rId299" xr:uid="{1EEDF26A-ED20-433B-AC23-3C86B9C9C1BE}"/>
+    <hyperlink ref="A301" r:id="rId300" xr:uid="{8BC0DAF3-1E52-4019-AC0C-990210FB154C}"/>
+    <hyperlink ref="A302" r:id="rId301" xr:uid="{75A34F36-E0A6-45AD-9FFB-C025F878C247}"/>
+    <hyperlink ref="A303" r:id="rId302" xr:uid="{69FF23DC-E6BA-4C71-9234-A55248F2D301}"/>
+    <hyperlink ref="A304" r:id="rId303" xr:uid="{C4E4A66F-4936-486B-A544-91580AC03F11}"/>
+    <hyperlink ref="A305" r:id="rId304" xr:uid="{0C47CCC9-BF55-44A3-B1D7-C2E89C9A5269}"/>
+    <hyperlink ref="A306" r:id="rId305" xr:uid="{A78B251A-1480-4047-9EDB-F331FA217F20}"/>
+    <hyperlink ref="A307" r:id="rId306" xr:uid="{6B7D609C-ADC8-49A9-8A32-27D0C09547B9}"/>
+    <hyperlink ref="A308" r:id="rId307" xr:uid="{D34DB2C2-8A53-4A14-8CCF-A3FD81FBB053}"/>
+    <hyperlink ref="A309" r:id="rId308" xr:uid="{A2175CE9-E452-4D88-A8A8-7E2E693F0524}"/>
+    <hyperlink ref="A310" r:id="rId309" xr:uid="{4485A09F-44AF-4AC7-8D59-B2DEC9D880D5}"/>
+    <hyperlink ref="A311" r:id="rId310" xr:uid="{8FCF2A7C-E140-450E-96A4-25E605B01706}"/>
+    <hyperlink ref="A312" r:id="rId311" xr:uid="{E181AF4D-C599-4765-9CB0-F78F3F083BC6}"/>
+    <hyperlink ref="A313" r:id="rId312" xr:uid="{15C29D4A-70ED-4605-8137-8AE10424E013}"/>
+    <hyperlink ref="A314" r:id="rId313" xr:uid="{9FEACBFD-7AE0-4D1B-8F1B-444E9D15AA0F}"/>
+    <hyperlink ref="A315" r:id="rId314" xr:uid="{03AC230E-DA9C-49F1-B570-E08D6F7457E5}"/>
+    <hyperlink ref="A316" r:id="rId315" xr:uid="{85DD4CE6-717F-468F-8529-A07698934F92}"/>
+    <hyperlink ref="A317" r:id="rId316" xr:uid="{A6C7EBB5-C12F-4363-B749-A65C82E737A1}"/>
+    <hyperlink ref="A318" r:id="rId317" xr:uid="{6F3CC06F-50D3-46D3-AF54-697AC5D0E886}"/>
+    <hyperlink ref="A319" r:id="rId318" xr:uid="{BCA8438A-51CC-4A0D-8FDA-50EBF917E782}"/>
+    <hyperlink ref="A320" r:id="rId319" xr:uid="{727C2BA3-243D-4558-966A-DBF69AE0D055}"/>
+    <hyperlink ref="A321" r:id="rId320" xr:uid="{9D0D6EB3-8A32-4C23-BBF3-591112CE6B26}"/>
+    <hyperlink ref="A322" r:id="rId321" xr:uid="{239F39B1-E2EE-47D8-B88D-CE1651E0D12E}"/>
+    <hyperlink ref="A323" r:id="rId322" xr:uid="{E116C9C2-D877-4A7A-B79D-8AC26BEF68EB}"/>
+    <hyperlink ref="A324" r:id="rId323" xr:uid="{2C028E51-9E36-4A31-88BF-47C0F315CA1E}"/>
+    <hyperlink ref="A325" r:id="rId324" xr:uid="{C9B15AC5-D4C5-4A68-A686-0C2CB44F0B9A}"/>
+    <hyperlink ref="A326" r:id="rId325" xr:uid="{DC1C6D37-548A-4EFF-88F2-413ECC2F5E39}"/>
+    <hyperlink ref="A327" r:id="rId326" xr:uid="{49F0B889-FC3A-4080-9438-E5FEAFB64427}"/>
+    <hyperlink ref="A328" r:id="rId327" xr:uid="{C1749765-D5CB-4D8D-B114-C9699FD0BB1F}"/>
+    <hyperlink ref="A329" r:id="rId328" xr:uid="{DDD4CBCE-FBB1-47A1-A5EF-D75FFBF74B3F}"/>
+    <hyperlink ref="A330" r:id="rId329" xr:uid="{3581FF3D-212B-4A6A-A3A2-56F75A58DD9F}"/>
+    <hyperlink ref="A331" r:id="rId330" xr:uid="{985AA089-6BA9-413D-8183-88A8E8F4E61F}"/>
+    <hyperlink ref="A332" r:id="rId331" xr:uid="{A9A1B631-8F85-47BC-AFC4-607A767A41A1}"/>
+    <hyperlink ref="A333" r:id="rId332" xr:uid="{38827C6A-F565-49CD-A3FB-C1911F4A47DD}"/>
+    <hyperlink ref="A334" r:id="rId333" xr:uid="{A7C76A0D-10B8-4D00-B598-C58CD47F837A}"/>
+    <hyperlink ref="A335" r:id="rId334" xr:uid="{0173BE5A-1B51-44B6-808D-8E31FA4F7F64}"/>
+    <hyperlink ref="A336" r:id="rId335" xr:uid="{BFA8F8FB-CA9F-426A-AC57-22362BF8B6A0}"/>
+    <hyperlink ref="A337" r:id="rId336" xr:uid="{A8468DCE-F520-4054-BCF4-C73D5464B9C7}"/>
+    <hyperlink ref="A338" r:id="rId337" xr:uid="{1B4B9A62-DB41-4513-80AB-0EF8BB45D60A}"/>
+    <hyperlink ref="A339" r:id="rId338" xr:uid="{5167942C-68CB-462C-833D-9793D7ECE464}"/>
+    <hyperlink ref="A340" r:id="rId339" xr:uid="{5B1DCE7B-0340-4FD3-9EC1-8CDA04704BD8}"/>
+    <hyperlink ref="A341" r:id="rId340" xr:uid="{BD801AAA-6E25-42A2-AD83-74B08CCF1C23}"/>
+    <hyperlink ref="A342" r:id="rId341" xr:uid="{F62AD526-F646-4FA2-B8C8-8C0A0DDC2226}"/>
+    <hyperlink ref="A343" r:id="rId342" xr:uid="{5A05CB46-D4C1-4A7B-A6DE-555FE96554D0}"/>
+    <hyperlink ref="A344" r:id="rId343" xr:uid="{3F7BB59D-2D8E-4928-BCAB-EB75EC7AF1FD}"/>
+    <hyperlink ref="A345" r:id="rId344" xr:uid="{DD31F9C7-D7DC-481A-ABC8-DE95F5D7593E}"/>
+    <hyperlink ref="A346" r:id="rId345" xr:uid="{DEB354FB-1B45-417B-BECC-A9E153E27539}"/>
+    <hyperlink ref="A347" r:id="rId346" xr:uid="{464B4CE1-1E59-4328-98FD-44B8A7D0C765}"/>
+    <hyperlink ref="A348" r:id="rId347" xr:uid="{2754C470-ACDA-4C7D-9AD9-A28104A54D1B}"/>
+    <hyperlink ref="A349" r:id="rId348" xr:uid="{048562E7-DA71-4731-BBFC-A5C089C77D9A}"/>
+    <hyperlink ref="A350" r:id="rId349" xr:uid="{C69A9C31-1DD9-4999-9DD3-86C2C600E4C1}"/>
+    <hyperlink ref="A351" r:id="rId350" xr:uid="{B5744B46-C541-450B-BB73-99936E6A96F6}"/>
+    <hyperlink ref="A352" r:id="rId351" xr:uid="{EE9A4A26-7079-495E-874C-CA93DEBCF07A}"/>
+    <hyperlink ref="A353" r:id="rId352" xr:uid="{AFB4F293-9FD9-42C3-9EA9-95DB09161304}"/>
+    <hyperlink ref="A354" r:id="rId353" xr:uid="{DA907C22-3770-49A7-B1A9-96F09585BF35}"/>
+    <hyperlink ref="A355" r:id="rId354" xr:uid="{14954825-0856-4E23-9A57-C7C5C4312176}"/>
+    <hyperlink ref="A356" r:id="rId355" xr:uid="{78AF8582-30EA-4887-9F32-0F6EEF2BD73B}"/>
+    <hyperlink ref="A357" r:id="rId356" xr:uid="{A4E8B726-DE14-4582-AB47-E5B410E354AB}"/>
+    <hyperlink ref="A358" r:id="rId357" xr:uid="{27CA8EE5-0B5E-486B-9590-52D01EF90037}"/>
+    <hyperlink ref="A359" r:id="rId358" xr:uid="{FA30B9F4-2AFC-40B4-AA13-5C91E35D2D05}"/>
+    <hyperlink ref="A360" r:id="rId359" xr:uid="{B5DA4C0B-C79C-48B3-909A-8A459836AD86}"/>
+    <hyperlink ref="A361" r:id="rId360" xr:uid="{C3287380-78F1-48EE-BF45-CAA8F992A0D1}"/>
+    <hyperlink ref="A362" r:id="rId361" xr:uid="{EC0C5D31-FFB3-4611-91AE-F0416C7FE9F5}"/>
+    <hyperlink ref="A363" r:id="rId362" xr:uid="{001A8EAB-E65E-4C48-A2C0-5D5F1FDAAFDF}"/>
+    <hyperlink ref="A364" r:id="rId363" xr:uid="{C3E9792E-5B5A-43E7-B6BC-8C1EE86AE8B3}"/>
+    <hyperlink ref="A365" r:id="rId364" xr:uid="{2F5AEB96-F31A-48A1-88FD-37FAD08880DE}"/>
+    <hyperlink ref="A366" r:id="rId365" xr:uid="{03C2C2BB-CC30-4EAC-BB70-C0C9DDAE9CF7}"/>
+    <hyperlink ref="A367" r:id="rId366" xr:uid="{71859367-BACE-46F5-9279-40298EE6ABFF}"/>
+    <hyperlink ref="A368" r:id="rId367" xr:uid="{1DE75026-8E74-4A92-B4CC-336D780BA84B}"/>
+    <hyperlink ref="A369" r:id="rId368" xr:uid="{B85B8F66-24AC-4146-B7EF-B4C837FBCB75}"/>
+    <hyperlink ref="A370" r:id="rId369" xr:uid="{F135F458-F275-43C8-9A15-7EA45BFBFB50}"/>
+    <hyperlink ref="A371" r:id="rId370" xr:uid="{E06DB9FA-D778-4B71-9646-6D64C5EA4B05}"/>
+    <hyperlink ref="A372" r:id="rId371" xr:uid="{7D55C40F-B637-49C3-BA93-8F401B929953}"/>
+    <hyperlink ref="A373" r:id="rId372" xr:uid="{9C0D6F65-3402-4258-81D5-002495F1BB0B}"/>
+    <hyperlink ref="A374" r:id="rId373" xr:uid="{7D99C572-3C8B-4C54-BAD6-AA44467BA634}"/>
+    <hyperlink ref="A375" r:id="rId374" xr:uid="{07FD7018-338A-4069-A6C8-85A8FE43D401}"/>
+    <hyperlink ref="A376" r:id="rId375" xr:uid="{FCE56027-8F63-4266-84DB-B02F6B17C63C}"/>
+    <hyperlink ref="A377" r:id="rId376" xr:uid="{827DBCE8-B4FF-4766-9F47-A87719B29281}"/>
+    <hyperlink ref="A378" r:id="rId377" xr:uid="{A72B70D9-915C-49DB-B9C0-19F01FD7E979}"/>
+    <hyperlink ref="A379" r:id="rId378" xr:uid="{FDCD76D2-253C-43B7-A79E-26AA06617E60}"/>
+    <hyperlink ref="A380" r:id="rId379" xr:uid="{C97EA1CD-5CC9-45A9-B219-887296E72775}"/>
+    <hyperlink ref="A381" r:id="rId380" xr:uid="{36C4D03D-A402-42A7-84A2-D35BA54A3494}"/>
+    <hyperlink ref="A382" r:id="rId381" xr:uid="{9E35A71B-B94F-49E7-8A39-DC4E9CF027C8}"/>
+    <hyperlink ref="A383" r:id="rId382" xr:uid="{76F8B662-9C6B-412A-B0EC-1349B5270DA3}"/>
+    <hyperlink ref="A384" r:id="rId383" xr:uid="{965FF437-2569-4917-98F9-F82DD8FE6FDA}"/>
+    <hyperlink ref="A385" r:id="rId384" xr:uid="{9F7F27B2-81EB-492E-804E-B3AFB13B9067}"/>
+    <hyperlink ref="A386" r:id="rId385" xr:uid="{09EA0C78-C560-47F9-99C3-C4852EF232D1}"/>
+    <hyperlink ref="A387" r:id="rId386" xr:uid="{8DA69B33-48CB-4F04-9E0B-25EAAB30E9BF}"/>
+    <hyperlink ref="A388" r:id="rId387" xr:uid="{AE943047-545C-4134-A242-D83DFF282E13}"/>
+    <hyperlink ref="A389" r:id="rId388" xr:uid="{D8DD3959-3ABC-48B9-AD52-885895240501}"/>
+    <hyperlink ref="A390" r:id="rId389" xr:uid="{4142DA63-5D17-41F7-A781-D08EF9008E3B}"/>
+    <hyperlink ref="A391" r:id="rId390" xr:uid="{ADDA1225-9010-4356-BD05-28BB5ED9BC2E}"/>
+    <hyperlink ref="A392" r:id="rId391" xr:uid="{28C5A4EE-26A6-4279-A976-860AFF522C6E}"/>
+    <hyperlink ref="A393" r:id="rId392" xr:uid="{087D4285-4691-4BEF-9847-6C8B6737128C}"/>
+    <hyperlink ref="A394" r:id="rId393" xr:uid="{E8A77651-5FBF-4194-8B06-6CE9301812B5}"/>
+    <hyperlink ref="A395" r:id="rId394" xr:uid="{C255A252-42B4-4571-99C0-433F55E3E63A}"/>
+    <hyperlink ref="A396" r:id="rId395" xr:uid="{ABACB7BF-3DE5-43BD-A325-E44BE7CBFD80}"/>
+    <hyperlink ref="A397" r:id="rId396" xr:uid="{A39EC9E9-DCA7-46EB-BEAF-C9EBD9575D86}"/>
+    <hyperlink ref="A398" r:id="rId397" xr:uid="{769455EB-5A69-4DB2-96A9-63177565EAEB}"/>
+    <hyperlink ref="A399" r:id="rId398" xr:uid="{CE0A94C5-D505-4923-A1B5-FCC47C517617}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId329"/>
+    <tablePart r:id="rId399"/>
   </tableParts>
 </worksheet>
 </file>